--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.712173462899292</v>
+        <v>9.480210689739081</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.13703561080476</v>
+        <v>9.821545204576182</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.074880241041095</v>
+        <v>8.968208917483429</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.405115840619501</v>
+        <v>1.403520588828184</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.072861525880502e-25</v>
+        <v>4.083471942667364e-25</v>
       </c>
     </row>
     <row r="16">
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -634,63 +634,63 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1081.786131430616</v>
+        <v>639.9745723415496</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fleet value — Cape</t>
+          <t>Fleet value — Post-Panamax</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>268.8275361558434</v>
+        <v>409.68625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>+ Cash &amp; equivalents</t>
+          <t>Fleet value — Cape</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171.775</v>
+        <v>268.8275361558434</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Working capital (net)</t>
+          <t>+ Cash &amp; equivalents</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.791</v>
+        <v>171.775</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>- Total debt</t>
+          <t>+ Working capital (net)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-544</v>
+        <v>53.791</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>- Lease liabilities</t>
+          <t>- Total debt</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0</v>
+        <v>-544</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>- Newbuild commitments</t>
+          <t>- Lease liabilities</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -700,59 +700,69 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>- Newbuild commitments</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>+ Newbuild advances</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>100.04</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10">
+    <row r="11">
+      <c r="A11">
         <f> NAV total</f>
         <v/>
       </c>
-      <c r="B10" t="n">
-        <v>1032.219667586459</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Diluted shares</t>
-        </is>
-      </c>
       <c r="B11" t="n">
-        <v>101826580</v>
+        <v>1000.094358497393</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAV / share</t>
+          <t>Diluted shares</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10.13703561080476</v>
+        <v>101826580</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NAV / share (ex yard discount)</t>
+          <t>NAV / share</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.13703561080476</v>
+        <v>9.821545204576182</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>NAV / share (ex yard discount)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9.821545204576182</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Yard-discount impact / share</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -820,16 +830,16 @@
         <v>20775</v>
       </c>
       <c r="C2" t="n">
-        <v>20775</v>
+        <v>18678</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5357393177694861</v>
+        <v>0.4744596990294676</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1607217953308458</v>
+        <v>0.1423379097088402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1565827911704419</v>
+        <v>0.1386723384074785</v>
       </c>
     </row>
     <row r="3">
@@ -842,16 +852,16 @@
         <v>19500</v>
       </c>
       <c r="C3" t="n">
-        <v>19500</v>
+        <v>18168</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4969663986554395</v>
+        <v>0.4602309598338666</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1490899195966318</v>
+        <v>0.13806928795016</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1415098892712403</v>
+        <v>0.1310495686257485</v>
       </c>
     </row>
     <row r="4">
@@ -864,16 +874,16 @@
         <v>17000</v>
       </c>
       <c r="C4" t="n">
-        <v>17000</v>
+        <v>17168</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3997925934466227</v>
+        <v>0.4111829976023942</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1199377780339868</v>
+        <v>0.1233548992807183</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1109082275406755</v>
+        <v>0.1140680898207586</v>
       </c>
     </row>
     <row r="5">
@@ -886,16 +896,16 @@
         <v>16500</v>
       </c>
       <c r="C5" t="n">
-        <v>16500</v>
+        <v>16968</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3747636422631497</v>
+        <v>0.3957792150143902</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1124290926789449</v>
+        <v>0.1187337645043171</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1012874708819324</v>
+        <v>0.1069673554092946</v>
       </c>
     </row>
     <row r="6">
@@ -908,16 +918,16 @@
         <v>15800</v>
       </c>
       <c r="C6" t="n">
-        <v>15800</v>
+        <v>16688</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3434115876227995</v>
+        <v>0.3779023964076962</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1030234762868398</v>
+        <v>0.1133707189223089</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09042374223137151</v>
+        <v>0.09950552081812869</v>
       </c>
     </row>
     <row r="7">
@@ -930,16 +940,16 @@
         <v>15400</v>
       </c>
       <c r="C7" t="n">
-        <v>15400</v>
+        <v>16528</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3276916498619515</v>
+        <v>0.3698825935232235</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09830749495858546</v>
+        <v>0.110964778056967</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08406247286697284</v>
+        <v>0.09488568138709162</v>
       </c>
     </row>
     <row r="8">
@@ -952,16 +962,16 @@
         <v>14800</v>
       </c>
       <c r="C8" t="n">
-        <v>14800</v>
+        <v>16288</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3056486086442263</v>
+        <v>0.3593897546200608</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09169458259326788</v>
+        <v>0.1078169263860183</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07638858493776386</v>
+        <v>0.08981972768772564</v>
       </c>
     </row>
     <row r="9">
@@ -974,16 +984,16 @@
         <v>14500</v>
       </c>
       <c r="C9" t="n">
-        <v>14500</v>
+        <v>16168</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2930902226118171</v>
+        <v>0.352606469744933</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08792706678354512</v>
+        <v>0.1057819409234799</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07136357989087339</v>
+        <v>0.08585499628559361</v>
       </c>
     </row>
     <row r="10">
@@ -993,7 +1003,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.8325267587912717</v>
+        <v>0.8608232784418196</v>
       </c>
     </row>
     <row r="11">
@@ -1003,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.42384483549056</v>
+        <v>10.25315525533448</v>
       </c>
       <c r="F11" t="n">
-        <v>8.242353482249824</v>
+        <v>8.10738563904161</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.074880241041095</v>
+        <v>8.968208917483429</v>
       </c>
     </row>
     <row r="13">
@@ -1044,9 +1054,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1090,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.848775830150836</v>
+        <v>6.926146842032286</v>
       </c>
       <c r="C2" t="n">
-        <v>8.005071887536239</v>
+        <v>8.055362070147702</v>
       </c>
       <c r="D2" t="n">
-        <v>9.161367944921643</v>
+        <v>9.184577298263118</v>
       </c>
       <c r="E2" t="n">
-        <v>10.31766400230705</v>
+        <v>10.31379252637853</v>
       </c>
       <c r="F2" t="n">
-        <v>11.47396005969245</v>
+        <v>11.44300775449395</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.12417858913966</v>
+        <v>7.073963537770267</v>
       </c>
       <c r="C3" t="n">
-        <v>8.280474646525064</v>
+        <v>8.203178765885685</v>
       </c>
       <c r="D3" t="n">
-        <v>9.436770703910469</v>
+        <v>9.3323939940011</v>
       </c>
       <c r="E3" t="n">
-        <v>10.59306676129587</v>
+        <v>10.46160922211651</v>
       </c>
       <c r="F3" t="n">
-        <v>11.74936281868128</v>
+        <v>11.59082445023193</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.399581348128486</v>
+        <v>7.221780233508249</v>
       </c>
       <c r="C4" t="n">
-        <v>8.555877405513888</v>
+        <v>8.350995461623665</v>
       </c>
       <c r="D4" t="n">
-        <v>9.712173462899292</v>
+        <v>9.480210689739081</v>
       </c>
       <c r="E4" t="n">
-        <v>10.8684695202847</v>
+        <v>10.60942591785449</v>
       </c>
       <c r="F4" t="n">
-        <v>12.0247655776701</v>
+        <v>11.73864114596991</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.674984107117309</v>
+        <v>7.369596929246231</v>
       </c>
       <c r="C5" t="n">
-        <v>8.831280164502713</v>
+        <v>8.498812157361648</v>
       </c>
       <c r="D5" t="n">
-        <v>9.987576221888117</v>
+        <v>9.628027385477063</v>
       </c>
       <c r="E5" t="n">
-        <v>11.14387227927352</v>
+        <v>10.75724261359248</v>
       </c>
       <c r="F5" t="n">
-        <v>12.30016833665892</v>
+        <v>11.88645784170789</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.950386866106134</v>
+        <v>7.517413624984212</v>
       </c>
       <c r="C6" t="n">
-        <v>9.106682923491539</v>
+        <v>8.646628853099632</v>
       </c>
       <c r="D6" t="n">
-        <v>10.26297898087694</v>
+        <v>9.775844081215045</v>
       </c>
       <c r="E6" t="n">
-        <v>11.41927503826235</v>
+        <v>10.90505930933046</v>
       </c>
       <c r="F6" t="n">
-        <v>12.57557109564775</v>
+        <v>12.03427453744588</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.779999999999999</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.81</v>
+        <v>9.57</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.480210689739081</v>
+        <v>9.802188613337233</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.821545204576182</v>
+        <v>10.30855057648806</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.968208917483429</v>
+        <v>9.042645668610993</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.403520588828184</v>
+        <v>1.405951656083557</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.083471942667364e-25</v>
+        <v>4.067302309160725e-25</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>639.9745723415496</v>
+        <v>682.8709138049642</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>409.68625</v>
+        <v>416.38</v>
       </c>
     </row>
     <row r="4">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1000.094358497393</v>
+        <v>1049.684449960807</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9.821545204576182</v>
+        <v>10.30855057648806</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.821545204576182</v>
+        <v>10.30855057648806</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.25315525533448</v>
+        <v>10.3472930699141</v>
       </c>
       <c r="F11" t="n">
-        <v>8.10738563904161</v>
+        <v>8.181822390169174</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8.968208917483429</v>
+        <v>9.042645668610993</v>
       </c>
     </row>
     <row r="13">
@@ -1056,7 +1056,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.926146842032286</v>
+        <v>7.183729180910808</v>
       </c>
       <c r="C2" t="n">
-        <v>8.055362070147702</v>
+        <v>8.345142201386039</v>
       </c>
       <c r="D2" t="n">
-        <v>9.184577298263118</v>
+        <v>9.506555221861269</v>
       </c>
       <c r="E2" t="n">
-        <v>10.31379252637853</v>
+        <v>10.6679682423365</v>
       </c>
       <c r="F2" t="n">
-        <v>11.44300775449395</v>
+        <v>11.82938126281173</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.073963537770267</v>
+        <v>7.331545876648789</v>
       </c>
       <c r="C3" t="n">
-        <v>8.203178765885685</v>
+        <v>8.492958897124021</v>
       </c>
       <c r="D3" t="n">
-        <v>9.3323939940011</v>
+        <v>9.654371917599249</v>
       </c>
       <c r="E3" t="n">
-        <v>10.46160922211651</v>
+        <v>10.81578493807448</v>
       </c>
       <c r="F3" t="n">
-        <v>11.59082445023193</v>
+        <v>11.97719795854972</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.221780233508249</v>
+        <v>7.479362572386771</v>
       </c>
       <c r="C4" t="n">
-        <v>8.350995461623665</v>
+        <v>8.640775592862003</v>
       </c>
       <c r="D4" t="n">
-        <v>9.480210689739081</v>
+        <v>9.802188613337233</v>
       </c>
       <c r="E4" t="n">
-        <v>10.60942591785449</v>
+        <v>10.96360163381246</v>
       </c>
       <c r="F4" t="n">
-        <v>11.73864114596991</v>
+        <v>12.1250146542877</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.369596929246231</v>
+        <v>7.627179268124753</v>
       </c>
       <c r="C5" t="n">
-        <v>8.498812157361648</v>
+        <v>8.788592288599984</v>
       </c>
       <c r="D5" t="n">
-        <v>9.628027385477063</v>
+        <v>9.950005309075213</v>
       </c>
       <c r="E5" t="n">
-        <v>10.75724261359248</v>
+        <v>11.11141832955044</v>
       </c>
       <c r="F5" t="n">
-        <v>11.88645784170789</v>
+        <v>12.27283135002568</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.517413624984212</v>
+        <v>7.774995963862734</v>
       </c>
       <c r="C6" t="n">
-        <v>8.646628853099632</v>
+        <v>8.936408984337966</v>
       </c>
       <c r="D6" t="n">
-        <v>9.775844081215045</v>
+        <v>10.0978220048132</v>
       </c>
       <c r="E6" t="n">
-        <v>10.90505930933046</v>
+        <v>11.25923502528843</v>
       </c>
       <c r="F6" t="n">
-        <v>12.03427453744588</v>
+        <v>12.42064804576366</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.550000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.57</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.57</v>
+        <v>9.9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.39</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -12,7 +12,6 @@
     <sheet name="DivStrip" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Payout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Warnings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.802188613337233</v>
+        <v>10.29884388705176</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.30855057648806</v>
+        <v>10.60850229149113</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.042645668610993</v>
+        <v>9.834356280392695</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.405951656083557</v>
+        <v>1.420659075407336</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.067302309160725e-25</v>
+        <v>3.978118932444419e-25</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>682.8709138049642</v>
+        <v>1040.953971108862</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +703,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0</v>
+        <v>-227.5</v>
       </c>
     </row>
     <row r="10">
@@ -714,7 +713,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1049.684449960807</v>
+        <v>1080.227507264705</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.30855057648806</v>
+        <v>10.60850229149113</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.30855057648806</v>
+        <v>10.60850229149113</v>
       </c>
     </row>
     <row r="15">
@@ -833,13 +832,13 @@
         <v>18678</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4744596990294676</v>
+        <v>0.5684061047714652</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1423379097088402</v>
+        <v>0.1705218314314396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1386723384074785</v>
+        <v>0.1661304508580609</v>
       </c>
     </row>
     <row r="3">
@@ -855,13 +854,13 @@
         <v>18168</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4602309598338666</v>
+        <v>0.5505942736169671</v>
       </c>
       <c r="E3" t="n">
-        <v>0.13806928795016</v>
+        <v>0.1651782820850901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1310495686257485</v>
+        <v>0.1567802871657251</v>
       </c>
     </row>
     <row r="4">
@@ -877,13 +876,13 @@
         <v>17168</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4111829976023942</v>
+        <v>0.4945206408778532</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1233548992807183</v>
+        <v>0.148356192263356</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1140680898207586</v>
+        <v>0.1371871531916319</v>
       </c>
     </row>
     <row r="5">
@@ -899,13 +898,13 @@
         <v>16968</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3957792150143902</v>
+        <v>0.4777117241883209</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1187337645043171</v>
+        <v>0.1433135172564963</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1069673554092946</v>
+        <v>0.1291112768076543</v>
       </c>
     </row>
     <row r="6">
@@ -921,13 +920,13 @@
         <v>16688</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3779023964076962</v>
+        <v>0.4578677178394875</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1133707189223089</v>
+        <v>0.1373603153518462</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09950552081812869</v>
+        <v>0.1205611982419763</v>
       </c>
     </row>
     <row r="7">
@@ -943,13 +942,13 @@
         <v>16528</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3698825935232235</v>
+        <v>0.4487238076737919</v>
       </c>
       <c r="E7" t="n">
-        <v>0.110964778056967</v>
+        <v>0.1346171423021376</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09488568138709162</v>
+        <v>0.1151107540373206</v>
       </c>
     </row>
     <row r="8">
@@ -965,13 +964,13 @@
         <v>16288</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3593897546200608</v>
+        <v>0.4365448078487955</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1078169263860183</v>
+        <v>0.1309634423546386</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08981972768772564</v>
+        <v>0.109102541907244</v>
       </c>
     </row>
     <row r="9">
@@ -987,13 +986,13 @@
         <v>16168</v>
       </c>
       <c r="D9" t="n">
-        <v>0.352606469744933</v>
+        <v>0.4289184425127505</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1057819409234799</v>
+        <v>0.1286755327538252</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08585499628559361</v>
+        <v>0.1044359489926346</v>
       </c>
     </row>
     <row r="10">
@@ -1003,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.8608232784418196</v>
+        <v>1.038419611202247</v>
       </c>
     </row>
     <row r="11">
@@ -1013,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.3472930699141</v>
+        <v>11.12394405552915</v>
       </c>
       <c r="F11" t="n">
-        <v>8.181822390169174</v>
+        <v>8.795936669190448</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.042645668610993</v>
+        <v>9.834356280392695</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.183729180910808</v>
+        <v>6.997841837027531</v>
       </c>
       <c r="C2" t="n">
-        <v>8.345142201386039</v>
+        <v>8.481900463637309</v>
       </c>
       <c r="D2" t="n">
-        <v>9.506555221861269</v>
+        <v>9.965959090247082</v>
       </c>
       <c r="E2" t="n">
-        <v>10.6679682423365</v>
+        <v>11.45001771685686</v>
       </c>
       <c r="F2" t="n">
-        <v>11.82938126281173</v>
+        <v>12.93407634346664</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.331545876648789</v>
+        <v>7.16428423542987</v>
       </c>
       <c r="C3" t="n">
-        <v>8.492958897124021</v>
+        <v>8.648342862039646</v>
       </c>
       <c r="D3" t="n">
-        <v>9.654371917599249</v>
+        <v>10.13240148864942</v>
       </c>
       <c r="E3" t="n">
-        <v>10.81578493807448</v>
+        <v>11.6164601152592</v>
       </c>
       <c r="F3" t="n">
-        <v>11.97719795854972</v>
+        <v>13.10051874186898</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.479362572386771</v>
+        <v>7.330726633832207</v>
       </c>
       <c r="C4" t="n">
-        <v>8.640775592862003</v>
+        <v>8.814785260441985</v>
       </c>
       <c r="D4" t="n">
-        <v>9.802188613337233</v>
+        <v>10.29884388705176</v>
       </c>
       <c r="E4" t="n">
-        <v>10.96360163381246</v>
+        <v>11.78290251366153</v>
       </c>
       <c r="F4" t="n">
-        <v>12.1250146542877</v>
+        <v>13.26696114027132</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.627179268124753</v>
+        <v>7.497169032234547</v>
       </c>
       <c r="C5" t="n">
-        <v>8.788592288599984</v>
+        <v>8.981227658844324</v>
       </c>
       <c r="D5" t="n">
-        <v>9.950005309075213</v>
+        <v>10.4652862854541</v>
       </c>
       <c r="E5" t="n">
-        <v>11.11141832955044</v>
+        <v>11.94934491206387</v>
       </c>
       <c r="F5" t="n">
-        <v>12.27283135002568</v>
+        <v>13.43340353867366</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.774995963862734</v>
+        <v>7.663611430636886</v>
       </c>
       <c r="C6" t="n">
-        <v>8.936408984337966</v>
+        <v>9.147670057246662</v>
       </c>
       <c r="D6" t="n">
-        <v>10.0978220048132</v>
+        <v>10.63172868385644</v>
       </c>
       <c r="E6" t="n">
-        <v>11.25923502528843</v>
+        <v>12.11578731046621</v>
       </c>
       <c r="F6" t="n">
-        <v>12.42064804576366</v>
+        <v>13.59984593707599</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.869999999999999</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.890000000000001</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="4">
@@ -1254,38 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data validation warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
+        <v>10.41</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.29884388705176</v>
+        <v>10.16829545456023</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.60850229149113</v>
+        <v>10.46885221334679</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.834356280392695</v>
+        <v>9.717460316380381</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.420659075407336</v>
+        <v>1.420203898287445</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.978118932444419e-25</v>
+        <v>3.980949181033049e-25</v>
       </c>
     </row>
     <row r="16">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1040.953971108862</v>
+        <v>1026.733881254691</v>
       </c>
     </row>
     <row r="3">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1080.227507264705</v>
+        <v>1066.007417410534</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.60850229149113</v>
+        <v>10.46885221334679</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.60850229149113</v>
+        <v>10.46885221334679</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11.12394405552915</v>
+        <v>10.97610941177314</v>
       </c>
       <c r="F11" t="n">
-        <v>8.795936669190448</v>
+        <v>8.679040705178133</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.834356280392695</v>
+        <v>9.717460316380381</v>
       </c>
     </row>
     <row r="13">
@@ -1053,7 +1053,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.997841837027531</v>
+        <v>6.893403091034303</v>
       </c>
       <c r="C2" t="n">
-        <v>8.481900463637309</v>
+        <v>8.364406874394929</v>
       </c>
       <c r="D2" t="n">
-        <v>9.965959090247082</v>
+        <v>9.835410657755551</v>
       </c>
       <c r="E2" t="n">
-        <v>11.45001771685686</v>
+        <v>11.30641444111617</v>
       </c>
       <c r="F2" t="n">
-        <v>12.93407634346664</v>
+        <v>12.7774182244768</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.16428423542987</v>
+        <v>7.059845489436642</v>
       </c>
       <c r="C3" t="n">
-        <v>8.648342862039646</v>
+        <v>8.530849272797267</v>
       </c>
       <c r="D3" t="n">
-        <v>10.13240148864942</v>
+        <v>10.00185305615789</v>
       </c>
       <c r="E3" t="n">
-        <v>11.6164601152592</v>
+        <v>11.47285683951851</v>
       </c>
       <c r="F3" t="n">
-        <v>13.10051874186898</v>
+        <v>12.94386062287914</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.330726633832207</v>
+        <v>7.226287887838979</v>
       </c>
       <c r="C4" t="n">
-        <v>8.814785260441985</v>
+        <v>8.697291671199606</v>
       </c>
       <c r="D4" t="n">
-        <v>10.29884388705176</v>
+        <v>10.16829545456023</v>
       </c>
       <c r="E4" t="n">
-        <v>11.78290251366153</v>
+        <v>11.63929923792085</v>
       </c>
       <c r="F4" t="n">
-        <v>13.26696114027132</v>
+        <v>13.11030302128148</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.497169032234547</v>
+        <v>7.392730286241318</v>
       </c>
       <c r="C5" t="n">
-        <v>8.981227658844324</v>
+        <v>8.863734069601943</v>
       </c>
       <c r="D5" t="n">
-        <v>10.4652862854541</v>
+        <v>10.33473785296257</v>
       </c>
       <c r="E5" t="n">
-        <v>11.94934491206387</v>
+        <v>11.80574163632319</v>
       </c>
       <c r="F5" t="n">
-        <v>13.43340353867366</v>
+        <v>13.27674541968382</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.663611430636886</v>
+        <v>7.559172684643657</v>
       </c>
       <c r="C6" t="n">
-        <v>9.147670057246662</v>
+        <v>9.030176468004283</v>
       </c>
       <c r="D6" t="n">
-        <v>10.63172868385644</v>
+        <v>10.5011802513649</v>
       </c>
       <c r="E6" t="n">
-        <v>12.11578731046621</v>
+        <v>11.97218403472552</v>
       </c>
       <c r="F6" t="n">
-        <v>13.59984593707599</v>
+        <v>13.44318781808616</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>10.38</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>10.4</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>10.41</v>
+        <v>10.28</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.36</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.16829545456023</v>
+        <v>9.87360896298558</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.46885221334679</v>
+        <v>10.11565082780987</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.717460316380381</v>
+        <v>9.510546165749149</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.420203898287445</v>
+        <v>1.419149808970251</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.980949181033049e-25</v>
+        <v>3.988321759395178e-25</v>
       </c>
     </row>
     <row r="16">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1026.733881254691</v>
+        <v>985.068592114204</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>416.38</v>
+        <v>422.08</v>
       </c>
     </row>
     <row r="4">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1066.007417410534</v>
+        <v>1030.042128270048</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.46885221334679</v>
+        <v>10.11565082780987</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.46885221334679</v>
+        <v>10.11565082780987</v>
       </c>
     </row>
     <row r="15">
@@ -829,16 +829,16 @@
         <v>20775</v>
       </c>
       <c r="C2" t="n">
-        <v>18678</v>
+        <v>18657</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5684061047714652</v>
+        <v>0.5809823887891059</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1705218314314396</v>
+        <v>0.1742947166367318</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1661304508580609</v>
+        <v>0.1698061744585484</v>
       </c>
     </row>
     <row r="3">
@@ -851,16 +851,16 @@
         <v>19500</v>
       </c>
       <c r="C3" t="n">
-        <v>18168</v>
+        <v>18147</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5505942736169671</v>
+        <v>0.5621740101835394</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1651782820850901</v>
+        <v>0.1686522030550618</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1567802871657251</v>
+        <v>0.160077587030986</v>
       </c>
     </row>
     <row r="4">
@@ -873,16 +873,16 @@
         <v>17000</v>
       </c>
       <c r="C4" t="n">
-        <v>17168</v>
+        <v>17147</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4945206408778532</v>
+        <v>0.5041463628344878</v>
       </c>
       <c r="E4" t="n">
-        <v>0.148356192263356</v>
+        <v>0.1512439088503463</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1371871531916319</v>
+        <v>0.1398574671957162</v>
       </c>
     </row>
     <row r="5">
@@ -895,16 +895,16 @@
         <v>16500</v>
       </c>
       <c r="C5" t="n">
-        <v>16968</v>
+        <v>16947</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4777117241883209</v>
+        <v>0.4869466432229678</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1433135172564963</v>
+        <v>0.1460839929668903</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1291112768076543</v>
+        <v>0.1316072008710724</v>
       </c>
     </row>
     <row r="6">
@@ -917,16 +917,16 @@
         <v>15800</v>
       </c>
       <c r="C6" t="n">
-        <v>16688</v>
+        <v>16667</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4578677178394875</v>
+        <v>0.4665555127833517</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1373603153518462</v>
+        <v>0.1399666538350055</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1205611982419763</v>
+        <v>0.1228487824670779</v>
       </c>
     </row>
     <row r="7">
@@ -939,16 +939,16 @@
         <v>15400</v>
       </c>
       <c r="C7" t="n">
-        <v>16528</v>
+        <v>16507</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4487238076737919</v>
+        <v>0.4570989602800664</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1346171423021376</v>
+        <v>0.1371296880840199</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1151107540373206</v>
+        <v>0.1172592251351294</v>
       </c>
     </row>
     <row r="8">
@@ -961,16 +961,16 @@
         <v>14800</v>
       </c>
       <c r="C8" t="n">
-        <v>16288</v>
+        <v>16267</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4365448078487955</v>
+        <v>0.4444509969486846</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1309634423546386</v>
+        <v>0.1333352990846054</v>
       </c>
       <c r="F8" t="n">
-        <v>0.109102541907244</v>
+        <v>0.1110784795706602</v>
       </c>
     </row>
     <row r="9">
@@ -983,16 +983,16 @@
         <v>14500</v>
       </c>
       <c r="C9" t="n">
-        <v>16168</v>
+        <v>16147</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4289184425127505</v>
+        <v>0.4365901498594472</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1286755327538252</v>
+        <v>0.1309770449578342</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1044359489926346</v>
+        <v>0.1063039079277933</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.038419611202247</v>
+        <v>1.058838824656984</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.97610941177314</v>
+        <v>10.68860806664576</v>
       </c>
       <c r="F11" t="n">
-        <v>8.679040705178133</v>
+        <v>8.451707341092165</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.717460316380381</v>
+        <v>9.510546165749149</v>
       </c>
     </row>
     <row r="13">
@@ -1053,7 +1053,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.893403091034303</v>
+        <v>6.652277030728944</v>
       </c>
       <c r="C2" t="n">
-        <v>8.364406874394929</v>
+        <v>8.0913203249014</v>
       </c>
       <c r="D2" t="n">
-        <v>9.835410657755551</v>
+        <v>9.530363619073853</v>
       </c>
       <c r="E2" t="n">
-        <v>11.30641444111617</v>
+        <v>10.9694069132463</v>
       </c>
       <c r="F2" t="n">
-        <v>12.7774182244768</v>
+        <v>12.40845020741877</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.059845489436642</v>
+        <v>6.823899702684807</v>
       </c>
       <c r="C3" t="n">
-        <v>8.530849272797267</v>
+        <v>8.262942996857262</v>
       </c>
       <c r="D3" t="n">
-        <v>10.00185305615789</v>
+        <v>9.701986291029717</v>
       </c>
       <c r="E3" t="n">
-        <v>11.47285683951851</v>
+        <v>11.14102958520217</v>
       </c>
       <c r="F3" t="n">
-        <v>12.94386062287914</v>
+        <v>12.58007287937463</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.226287887838979</v>
+        <v>6.99552237464067</v>
       </c>
       <c r="C4" t="n">
-        <v>8.697291671199606</v>
+        <v>8.434565668813125</v>
       </c>
       <c r="D4" t="n">
-        <v>10.16829545456023</v>
+        <v>9.87360896298558</v>
       </c>
       <c r="E4" t="n">
-        <v>11.63929923792085</v>
+        <v>11.31265225715803</v>
       </c>
       <c r="F4" t="n">
-        <v>13.11030302128148</v>
+        <v>12.75169555133049</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.392730286241318</v>
+        <v>7.167145046596531</v>
       </c>
       <c r="C5" t="n">
-        <v>8.863734069601943</v>
+        <v>8.606188340768988</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33473785296257</v>
+        <v>10.04523163494144</v>
       </c>
       <c r="E5" t="n">
-        <v>11.80574163632319</v>
+        <v>11.48427492911389</v>
       </c>
       <c r="F5" t="n">
-        <v>13.27674541968382</v>
+        <v>12.92331822328635</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.559172684643657</v>
+        <v>7.338767718552395</v>
       </c>
       <c r="C6" t="n">
-        <v>9.030176468004283</v>
+        <v>8.77781101272485</v>
       </c>
       <c r="D6" t="n">
-        <v>10.5011802513649</v>
+        <v>10.21685430689731</v>
       </c>
       <c r="E6" t="n">
-        <v>11.97218403472552</v>
+        <v>11.65589760106975</v>
       </c>
       <c r="F6" t="n">
-        <v>13.44318781808616</v>
+        <v>13.09494089524222</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>10.25</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>10.27</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>10.28</v>
+        <v>9.99</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.988321759395178e-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.87360896298558</v>
+        <v>9.751595999318253</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.510546165749149</v>
+        <v>8.902134732837819</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17500</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18443.75</v>
+        <v>17431.25</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.419149808970251</v>
+        <v>1.533921107896562</v>
       </c>
     </row>
     <row r="12">
@@ -552,7 +552,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20775</v>
+        <v>19000</v>
       </c>
       <c r="C2" t="n">
-        <v>18657</v>
+        <v>17947</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5809823887891059</v>
+        <v>0.5606503178921947</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1742947166367318</v>
+        <v>0.1681950953676584</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1698061744585484</v>
+        <v>0.1638636342982171</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19500</v>
+        <v>18125</v>
       </c>
       <c r="C3" t="n">
-        <v>18147</v>
+        <v>17597</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5621740101835394</v>
+        <v>0.5537574764675882</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1686522030550618</v>
+        <v>0.1661272429402764</v>
       </c>
       <c r="F3" t="n">
-        <v>0.160077587030986</v>
+        <v>0.1576810009490813</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17000</v>
+        <v>16600</v>
       </c>
       <c r="C4" t="n">
-        <v>17147</v>
+        <v>16987</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5041463628344878</v>
+        <v>0.5039110028724818</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1512439088503463</v>
+        <v>0.1511733008617445</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1398574671957162</v>
+        <v>0.1397921749500668</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16500</v>
+        <v>16000</v>
       </c>
       <c r="C5" t="n">
-        <v>16947</v>
+        <v>16747</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4869466432229678</v>
+        <v>0.4881893086940069</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1460839929668903</v>
+        <v>0.1464567926082021</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1316072008710724</v>
+        <v>0.1319430564037856</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15800</v>
+        <v>15400</v>
       </c>
       <c r="C6" t="n">
-        <v>16667</v>
+        <v>16507</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4665555127833517</v>
+        <v>0.4724676145155322</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1399666538350055</v>
+        <v>0.1417402843546596</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1228487824670779</v>
+        <v>0.1244054986127879</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15400</v>
+        <v>14800</v>
       </c>
       <c r="C7" t="n">
-        <v>16507</v>
+        <v>16267</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4570989602800664</v>
+        <v>0.4567459203370572</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1371296880840199</v>
+        <v>0.1370237761011172</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1172592251351294</v>
+        <v>0.1171686600852032</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14800</v>
+        <v>14400</v>
       </c>
       <c r="C8" t="n">
-        <v>16267</v>
+        <v>16107</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4444509969486846</v>
+        <v>0.4472893678337719</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1333352990846054</v>
+        <v>0.1341868103501316</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1110784795706602</v>
+        <v>0.1117878534376054</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14500</v>
+        <v>14100</v>
       </c>
       <c r="C9" t="n">
-        <v>16147</v>
+        <v>15987</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4365901498594472</v>
+        <v>0.4394285207445345</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1309770449578342</v>
+        <v>0.1318285562233603</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1063039079277933</v>
+        <v>0.1069950135730544</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.058838824656984</v>
+        <v>1.053636892309802</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.68860806664576</v>
+        <v>9.925748010872205</v>
       </c>
       <c r="F11" t="n">
-        <v>8.451707341092165</v>
+        <v>7.848497840528018</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.510546165749149</v>
+        <v>8.902134732837819</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18443.75</v>
+        <v>17431.25</v>
       </c>
     </row>
   </sheetData>
@@ -1053,7 +1053,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.652277030728944</v>
+        <v>6.549575757789735</v>
       </c>
       <c r="C2" t="n">
-        <v>8.0913203249014</v>
+        <v>8.022514075687354</v>
       </c>
       <c r="D2" t="n">
-        <v>9.530363619073853</v>
+        <v>9.495452393584973</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9694069132463</v>
+        <v>10.96839071148258</v>
       </c>
       <c r="F2" t="n">
-        <v>12.40845020741877</v>
+        <v>12.44132902938021</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.823899702684807</v>
+        <v>6.677647560656375</v>
       </c>
       <c r="C3" t="n">
-        <v>8.262942996857262</v>
+        <v>8.150585878553994</v>
       </c>
       <c r="D3" t="n">
-        <v>9.701986291029717</v>
+        <v>9.623524196451612</v>
       </c>
       <c r="E3" t="n">
-        <v>11.14102958520217</v>
+        <v>11.09646251434923</v>
       </c>
       <c r="F3" t="n">
-        <v>12.58007287937463</v>
+        <v>12.56940083224685</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.99552237464067</v>
+        <v>6.805719363523016</v>
       </c>
       <c r="C4" t="n">
-        <v>8.434565668813125</v>
+        <v>8.278657681420635</v>
       </c>
       <c r="D4" t="n">
-        <v>9.87360896298558</v>
+        <v>9.751595999318253</v>
       </c>
       <c r="E4" t="n">
-        <v>11.31265225715803</v>
+        <v>11.22453431721586</v>
       </c>
       <c r="F4" t="n">
-        <v>12.75169555133049</v>
+        <v>12.69747263511349</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.167145046596531</v>
+        <v>6.933791166389655</v>
       </c>
       <c r="C5" t="n">
-        <v>8.606188340768988</v>
+        <v>8.406729484287276</v>
       </c>
       <c r="D5" t="n">
-        <v>10.04523163494144</v>
+        <v>9.879667802184892</v>
       </c>
       <c r="E5" t="n">
-        <v>11.48427492911389</v>
+        <v>11.35260612008251</v>
       </c>
       <c r="F5" t="n">
-        <v>12.92331822328635</v>
+        <v>12.82554443798013</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.338767718552395</v>
+        <v>7.061862969256296</v>
       </c>
       <c r="C6" t="n">
-        <v>8.77781101272485</v>
+        <v>8.534801287153915</v>
       </c>
       <c r="D6" t="n">
-        <v>10.21685430689731</v>
+        <v>10.00773960505153</v>
       </c>
       <c r="E6" t="n">
-        <v>11.65589760106975</v>
+        <v>11.48067792294914</v>
       </c>
       <c r="F6" t="n">
-        <v>13.09494089524222</v>
+        <v>12.95361624084677</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.98</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.99</v>
+        <v>9.84</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.31</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.751595999318253</v>
+        <v>9.782951636324931</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.902134732837819</v>
+        <v>9.006653522860079</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18550</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17431.25</v>
+        <v>18137.5</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.533921107896562</v>
+        <v>1.615815856308098</v>
       </c>
     </row>
     <row r="12">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19000</v>
+        <v>19700</v>
       </c>
       <c r="C2" t="n">
-        <v>17947</v>
+        <v>18227</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5606503178921947</v>
+        <v>0.5896478947036716</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1681950953676584</v>
+        <v>0.1768943684111015</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1638636342982171</v>
+        <v>0.1723388784397606</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18125</v>
+        <v>19250</v>
       </c>
       <c r="C3" t="n">
-        <v>17597</v>
+        <v>18047</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5537574764675882</v>
+        <v>0.581237728001618</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1661272429402764</v>
+        <v>0.1743713184004854</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1576810009490813</v>
+        <v>0.1655059310897256</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16600</v>
+        <v>17100</v>
       </c>
       <c r="C4" t="n">
-        <v>16987</v>
+        <v>17187</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5039110028724818</v>
+        <v>0.5155780069592341</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1511733008617445</v>
+        <v>0.1546734020877702</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1397921749500668</v>
+        <v>0.143028770037575</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16000</v>
+        <v>16500</v>
       </c>
       <c r="C5" t="n">
-        <v>16747</v>
+        <v>16947</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4881893086940069</v>
+        <v>0.4998563127807591</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1464567926082021</v>
+        <v>0.1499568938342277</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1319430564037856</v>
+        <v>0.1350963007515565</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15400</v>
+        <v>15900</v>
       </c>
       <c r="C6" t="n">
-        <v>16507</v>
+        <v>16707</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4724676145155322</v>
+        <v>0.4841346186022844</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1417402843546596</v>
+        <v>0.1452403855806853</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1244054986127879</v>
+        <v>0.1274775387191096</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14800</v>
+        <v>15300</v>
       </c>
       <c r="C7" t="n">
-        <v>16267</v>
+        <v>16467</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4567459203370572</v>
+        <v>0.4684129244238094</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1370237761011172</v>
+        <v>0.1405238773271428</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1171686600852032</v>
+        <v>0.1201615871704513</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14400</v>
+        <v>14900</v>
       </c>
       <c r="C8" t="n">
-        <v>16107</v>
+        <v>16307</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4472893678337719</v>
+        <v>0.4589563719205241</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1341868103501316</v>
+        <v>0.1376869115761572</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1117878534376054</v>
+        <v>0.114703704867793</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14100</v>
+        <v>14600</v>
       </c>
       <c r="C9" t="n">
-        <v>15987</v>
+        <v>16187</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4394285207445345</v>
+        <v>0.4510955248312867</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1318285562233603</v>
+        <v>0.135328657449386</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1069950135730544</v>
+        <v>0.1098357742467218</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.053636892309802</v>
+        <v>1.088148485322693</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.925748010872205</v>
+        <v>10.01428390787842</v>
       </c>
       <c r="F11" t="n">
-        <v>7.848497840528018</v>
+        <v>7.918505037537386</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8.902134732837819</v>
+        <v>9.006653522860079</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17431.25</v>
+        <v>18137.5</v>
       </c>
     </row>
   </sheetData>
@@ -1053,7 +1053,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.549575757789735</v>
+        <v>6.57152470369441</v>
       </c>
       <c r="C2" t="n">
-        <v>8.022514075687354</v>
+        <v>8.044463021592028</v>
       </c>
       <c r="D2" t="n">
-        <v>9.495452393584973</v>
+        <v>9.517401339489647</v>
       </c>
       <c r="E2" t="n">
-        <v>10.96839071148258</v>
+        <v>10.99033965738726</v>
       </c>
       <c r="F2" t="n">
-        <v>12.44132902938021</v>
+        <v>12.46327797528488</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.677647560656375</v>
+        <v>6.704299852112052</v>
       </c>
       <c r="C3" t="n">
-        <v>8.150585878553994</v>
+        <v>8.177238170009669</v>
       </c>
       <c r="D3" t="n">
-        <v>9.623524196451612</v>
+        <v>9.650176487907288</v>
       </c>
       <c r="E3" t="n">
-        <v>11.09646251434923</v>
+        <v>11.1231148058049</v>
       </c>
       <c r="F3" t="n">
-        <v>12.56940083224685</v>
+        <v>12.59605312370253</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.805719363523016</v>
+        <v>6.837075000529694</v>
       </c>
       <c r="C4" t="n">
-        <v>8.278657681420635</v>
+        <v>8.310013318427313</v>
       </c>
       <c r="D4" t="n">
-        <v>9.751595999318253</v>
+        <v>9.782951636324931</v>
       </c>
       <c r="E4" t="n">
-        <v>11.22453431721586</v>
+        <v>11.25588995422254</v>
       </c>
       <c r="F4" t="n">
-        <v>12.69747263511349</v>
+        <v>12.72882827212017</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.933791166389655</v>
+        <v>6.969850148947335</v>
       </c>
       <c r="C5" t="n">
-        <v>8.406729484287276</v>
+        <v>8.442788466844954</v>
       </c>
       <c r="D5" t="n">
-        <v>9.879667802184892</v>
+        <v>9.915726784742573</v>
       </c>
       <c r="E5" t="n">
-        <v>11.35260612008251</v>
+        <v>11.38866510264018</v>
       </c>
       <c r="F5" t="n">
-        <v>12.82554443798013</v>
+        <v>12.86160342053781</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.061862969256296</v>
+        <v>7.102625297364978</v>
       </c>
       <c r="C6" t="n">
-        <v>8.534801287153915</v>
+        <v>8.575563615262595</v>
       </c>
       <c r="D6" t="n">
-        <v>10.00773960505153</v>
+        <v>10.04850193316021</v>
       </c>
       <c r="E6" t="n">
-        <v>11.48067792294914</v>
+        <v>11.52144025105783</v>
       </c>
       <c r="F6" t="n">
-        <v>12.95361624084677</v>
+        <v>12.99437856895545</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.81</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.83</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.84</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.9</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.96</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.13</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.782951636324931</v>
+        <v>9.823697951699195</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.11565082780987</v>
+        <v>10.16595773527163</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.006653522860079</v>
+        <v>9.025091790030176</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.615815856308098</v>
+        <v>1.615513780328368</v>
       </c>
     </row>
     <row r="12">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>985.068592114204</v>
+        <v>985.8240201495729</v>
       </c>
     </row>
     <row r="3">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>268.8275361558434</v>
+        <v>273.1946884576828</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1030.042128270048</v>
+        <v>1035.164708607256</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.11565082780987</v>
+        <v>10.16595773527163</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.11565082780987</v>
+        <v>10.16595773527163</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.01428390787842</v>
+        <v>10.03760220360916</v>
       </c>
       <c r="F11" t="n">
-        <v>7.918505037537386</v>
+        <v>7.936943304707484</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.006653522860079</v>
+        <v>9.025091790030176</v>
       </c>
     </row>
     <row r="13">
@@ -1055,7 +1055,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.57152470369441</v>
+        <v>6.604121755993822</v>
       </c>
       <c r="C2" t="n">
-        <v>8.044463021592028</v>
+        <v>8.081134705428868</v>
       </c>
       <c r="D2" t="n">
-        <v>9.517401339489647</v>
+        <v>9.558147654863912</v>
       </c>
       <c r="E2" t="n">
-        <v>10.99033965738726</v>
+        <v>11.03516060429896</v>
       </c>
       <c r="F2" t="n">
-        <v>12.46327797528488</v>
+        <v>12.512173553734</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.704299852112052</v>
+        <v>6.736896904411465</v>
       </c>
       <c r="C3" t="n">
-        <v>8.177238170009669</v>
+        <v>8.213909853846511</v>
       </c>
       <c r="D3" t="n">
-        <v>9.650176487907288</v>
+        <v>9.690922803281554</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1231148058049</v>
+        <v>11.1679357527166</v>
       </c>
       <c r="F3" t="n">
-        <v>12.59605312370253</v>
+        <v>12.64494870215164</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.837075000529694</v>
+        <v>6.869672052829106</v>
       </c>
       <c r="C4" t="n">
-        <v>8.310013318427313</v>
+        <v>8.346685002264152</v>
       </c>
       <c r="D4" t="n">
-        <v>9.782951636324931</v>
+        <v>9.823697951699195</v>
       </c>
       <c r="E4" t="n">
-        <v>11.25588995422254</v>
+        <v>11.30071090113424</v>
       </c>
       <c r="F4" t="n">
-        <v>12.72882827212017</v>
+        <v>12.77772385056929</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.969850148947335</v>
+        <v>7.002447201246748</v>
       </c>
       <c r="C5" t="n">
-        <v>8.442788466844954</v>
+        <v>8.479460150681794</v>
       </c>
       <c r="D5" t="n">
-        <v>9.915726784742573</v>
+        <v>9.956473100116838</v>
       </c>
       <c r="E5" t="n">
-        <v>11.38866510264018</v>
+        <v>11.43348604955188</v>
       </c>
       <c r="F5" t="n">
-        <v>12.86160342053781</v>
+        <v>12.91049899898693</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.102625297364978</v>
+        <v>7.135222349664391</v>
       </c>
       <c r="C6" t="n">
-        <v>8.575563615262595</v>
+        <v>8.612235299099435</v>
       </c>
       <c r="D6" t="n">
-        <v>10.04850193316021</v>
+        <v>10.08924824853448</v>
       </c>
       <c r="E6" t="n">
-        <v>11.52144025105783</v>
+        <v>11.56626119796952</v>
       </c>
       <c r="F6" t="n">
-        <v>12.99437856895545</v>
+        <v>13.04327414740457</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.85</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.869999999999999</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.91</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.823697951699195</v>
+        <v>9.693107203176782</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.16595773527163</v>
+        <v>10.0191838536759</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.025091790030176</v>
+        <v>8.932261685345516</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.615513780328368</v>
+        <v>1.61531143563127</v>
       </c>
     </row>
     <row r="12">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>422.08</v>
+        <v>407.1345176037811</v>
       </c>
     </row>
     <row r="4">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1035.164708607256</v>
+        <v>1020.219226211037</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.16595773527163</v>
+        <v>10.0191838536759</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.16595773527163</v>
+        <v>10.0191838536759</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.03760220360916</v>
+        <v>9.92020289413049</v>
       </c>
       <c r="F11" t="n">
-        <v>7.936943304707484</v>
+        <v>7.844113200022823</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.025091790030176</v>
+        <v>8.932261685345516</v>
       </c>
     </row>
     <row r="13">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.604121755993822</v>
+        <v>6.499649157175892</v>
       </c>
       <c r="C2" t="n">
-        <v>8.081134705428868</v>
+        <v>7.963603031758694</v>
       </c>
       <c r="D2" t="n">
-        <v>9.558147654863912</v>
+        <v>9.427556906341497</v>
       </c>
       <c r="E2" t="n">
-        <v>11.03516060429896</v>
+        <v>10.8915107809243</v>
       </c>
       <c r="F2" t="n">
-        <v>12.512173553734</v>
+        <v>12.35546465550711</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.736896904411465</v>
+        <v>6.632424305593533</v>
       </c>
       <c r="C3" t="n">
-        <v>8.213909853846511</v>
+        <v>8.096378180176337</v>
       </c>
       <c r="D3" t="n">
-        <v>9.690922803281554</v>
+        <v>9.56033205475914</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1679357527166</v>
+        <v>11.02428592934194</v>
       </c>
       <c r="F3" t="n">
-        <v>12.64494870215164</v>
+        <v>12.48823980392475</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.869672052829106</v>
+        <v>6.765199454011175</v>
       </c>
       <c r="C4" t="n">
-        <v>8.346685002264152</v>
+        <v>8.229153328593979</v>
       </c>
       <c r="D4" t="n">
-        <v>9.823697951699195</v>
+        <v>9.693107203176782</v>
       </c>
       <c r="E4" t="n">
-        <v>11.30071090113424</v>
+        <v>11.15706107775959</v>
       </c>
       <c r="F4" t="n">
-        <v>12.77772385056929</v>
+        <v>12.62101495234239</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.002447201246748</v>
+        <v>6.897974602428818</v>
       </c>
       <c r="C5" t="n">
-        <v>8.479460150681794</v>
+        <v>8.36192847701162</v>
       </c>
       <c r="D5" t="n">
-        <v>9.956473100116838</v>
+        <v>9.825882351594423</v>
       </c>
       <c r="E5" t="n">
-        <v>11.43348604955188</v>
+        <v>11.28983622617723</v>
       </c>
       <c r="F5" t="n">
-        <v>12.91049899898693</v>
+        <v>12.75379010076003</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.135222349664391</v>
+        <v>7.030749750846459</v>
       </c>
       <c r="C6" t="n">
-        <v>8.612235299099435</v>
+        <v>8.494703625429263</v>
       </c>
       <c r="D6" t="n">
-        <v>10.08924824853448</v>
+        <v>9.958657500012066</v>
       </c>
       <c r="E6" t="n">
-        <v>11.56626119796952</v>
+        <v>11.42261137459487</v>
       </c>
       <c r="F6" t="n">
-        <v>13.04327414740457</v>
+        <v>12.88656524917767</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.890000000000001</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.91</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.91</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.82</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.693107203176782</v>
+        <v>9.700745506950545</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.932261685345516</v>
+        <v>8.95772269792473</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19500</v>
+        <v>19150</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18137.5</v>
+        <v>18075</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.61531143563127</v>
+        <v>1.590600563269323</v>
       </c>
     </row>
     <row r="12">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19700</v>
+        <v>19150</v>
       </c>
       <c r="C2" t="n">
-        <v>18227</v>
+        <v>18007</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5896478947036716</v>
+        <v>0.577797784079314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1768943684111015</v>
+        <v>0.1733393352237942</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1723388784397606</v>
+        <v>0.1688753966013065</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19250</v>
+        <v>19100</v>
       </c>
       <c r="C3" t="n">
-        <v>18047</v>
+        <v>17987</v>
       </c>
       <c r="D3" t="n">
-        <v>0.581237728001618</v>
+        <v>0.5820715872699938</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1743713184004854</v>
+        <v>0.1746214761809981</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1655059310897256</v>
+        <v>0.1657433703472989</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17100</v>
+        <v>17325</v>
       </c>
       <c r="C4" t="n">
-        <v>17187</v>
+        <v>17277</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5155780069592341</v>
+        <v>0.5227031346149993</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1546734020877702</v>
+        <v>0.1568109403844998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.143028770037575</v>
+        <v>0.1450053831421083</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16500</v>
+        <v>16725</v>
       </c>
       <c r="C5" t="n">
-        <v>16947</v>
+        <v>17037</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4998563127807591</v>
+        <v>0.5069814404365245</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1499568938342277</v>
+        <v>0.1520944321309573</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1350963007515565</v>
+        <v>0.1370220109287904</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15900</v>
+        <v>16125</v>
       </c>
       <c r="C6" t="n">
-        <v>16707</v>
+        <v>16797</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4841346186022844</v>
+        <v>0.4912597462580496</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1452403855806853</v>
+        <v>0.1473779238774149</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1274775387191096</v>
+        <v>0.1293536568517866</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15300</v>
+        <v>15525</v>
       </c>
       <c r="C7" t="n">
-        <v>16467</v>
+        <v>16557</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4684129244238094</v>
+        <v>0.4755380520795749</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1405238773271428</v>
+        <v>0.1426614156238725</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1201615871704513</v>
+        <v>0.1219893903826748</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14900</v>
+        <v>15125</v>
       </c>
       <c r="C8" t="n">
-        <v>16307</v>
+        <v>16397</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4589563719205241</v>
+        <v>0.4660814995762893</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1376869115761572</v>
+        <v>0.1398244498728868</v>
       </c>
       <c r="F8" t="n">
-        <v>0.114703704867793</v>
+        <v>0.1164844373943996</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14600</v>
+        <v>14825</v>
       </c>
       <c r="C9" t="n">
-        <v>16187</v>
+        <v>16277</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4510955248312867</v>
+        <v>0.458220652487052</v>
       </c>
       <c r="E9" t="n">
-        <v>0.135328657449386</v>
+        <v>0.1374661957461156</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1098357742467218</v>
+        <v>0.1115706482802658</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.088148485322693</v>
+        <v>1.096044293928631</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.92020289413049</v>
+        <v>9.942417054335518</v>
       </c>
       <c r="F11" t="n">
-        <v>7.844113200022823</v>
+        <v>7.861678403996098</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8.932261685345516</v>
+        <v>8.95772269792473</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18137.5</v>
+        <v>18075</v>
       </c>
     </row>
   </sheetData>
@@ -1054,7 +1054,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.499649157175892</v>
+        <v>6.504995969817527</v>
       </c>
       <c r="C2" t="n">
-        <v>7.963603031758694</v>
+        <v>7.968949844400329</v>
       </c>
       <c r="D2" t="n">
-        <v>9.427556906341497</v>
+        <v>9.432903718983132</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8915107809243</v>
+        <v>10.89685759356594</v>
       </c>
       <c r="F2" t="n">
-        <v>12.35546465550711</v>
+        <v>12.36081146814874</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.632424305593533</v>
+        <v>6.638916863801233</v>
       </c>
       <c r="C3" t="n">
-        <v>8.096378180176337</v>
+        <v>8.102870738384036</v>
       </c>
       <c r="D3" t="n">
-        <v>9.56033205475914</v>
+        <v>9.566824612966839</v>
       </c>
       <c r="E3" t="n">
-        <v>11.02428592934194</v>
+        <v>11.03077848754964</v>
       </c>
       <c r="F3" t="n">
-        <v>12.48823980392475</v>
+        <v>12.49473236213245</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.765199454011175</v>
+        <v>6.772837757784939</v>
       </c>
       <c r="C4" t="n">
-        <v>8.229153328593979</v>
+        <v>8.236791632367742</v>
       </c>
       <c r="D4" t="n">
-        <v>9.693107203176782</v>
+        <v>9.700745506950545</v>
       </c>
       <c r="E4" t="n">
-        <v>11.15706107775959</v>
+        <v>11.16469938153335</v>
       </c>
       <c r="F4" t="n">
-        <v>12.62101495234239</v>
+        <v>12.62865325611615</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.897974602428818</v>
+        <v>6.906758651768646</v>
       </c>
       <c r="C5" t="n">
-        <v>8.36192847701162</v>
+        <v>8.370712526351449</v>
       </c>
       <c r="D5" t="n">
-        <v>9.825882351594423</v>
+        <v>9.834666400934251</v>
       </c>
       <c r="E5" t="n">
-        <v>11.28983622617723</v>
+        <v>11.29862027551706</v>
       </c>
       <c r="F5" t="n">
-        <v>12.75379010076003</v>
+        <v>12.76257415009986</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.030749750846459</v>
+        <v>7.040679545752353</v>
       </c>
       <c r="C6" t="n">
-        <v>8.494703625429263</v>
+        <v>8.504633420335155</v>
       </c>
       <c r="D6" t="n">
-        <v>9.958657500012066</v>
+        <v>9.968587294917958</v>
       </c>
       <c r="E6" t="n">
-        <v>11.42261137459487</v>
+        <v>11.43254116950076</v>
       </c>
       <c r="F6" t="n">
-        <v>12.88656524917767</v>
+        <v>12.89649504408357</v>
       </c>
     </row>
   </sheetData>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.16</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.700745506950545</v>
+        <v>9.750573101563386</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.0191838536759</v>
+        <v>10.07159324337377</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.95772269792473</v>
+        <v>9.001526104005823</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.590600563269323</v>
+        <v>1.590500434799238</v>
       </c>
     </row>
     <row r="12">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>985.8240201495729</v>
+        <v>988.8358734426331</v>
       </c>
     </row>
     <row r="3">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>273.1946884576828</v>
+        <v>275.5195040774443</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1020.219226211037</v>
+        <v>1025.555895123859</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.0191838536759</v>
+        <v>10.07159324337377</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.0191838536759</v>
+        <v>10.07159324337377</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.942417054335518</v>
+        <v>9.99781384230859</v>
       </c>
       <c r="F11" t="n">
-        <v>7.861678403996098</v>
+        <v>7.905481810077192</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8.95772269792473</v>
+        <v>9.001526104005823</v>
       </c>
     </row>
     <row r="13">
@@ -1053,8 +1053,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.504995969817527</v>
+        <v>6.544858045507796</v>
       </c>
       <c r="C2" t="n">
-        <v>7.968949844400329</v>
+        <v>8.013794679551886</v>
       </c>
       <c r="D2" t="n">
-        <v>9.432903718983132</v>
+        <v>9.482731313595973</v>
       </c>
       <c r="E2" t="n">
-        <v>10.89685759356594</v>
+        <v>10.95166794764006</v>
       </c>
       <c r="F2" t="n">
-        <v>12.36081146814874</v>
+        <v>12.42060458168415</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.638916863801233</v>
+        <v>6.678778939491503</v>
       </c>
       <c r="C3" t="n">
-        <v>8.102870738384036</v>
+        <v>8.147715573535594</v>
       </c>
       <c r="D3" t="n">
-        <v>9.566824612966839</v>
+        <v>9.61665220757968</v>
       </c>
       <c r="E3" t="n">
-        <v>11.03077848754964</v>
+        <v>11.08558884162377</v>
       </c>
       <c r="F3" t="n">
-        <v>12.49473236213245</v>
+        <v>12.55452547566786</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.772837757784939</v>
+        <v>6.812699833475209</v>
       </c>
       <c r="C4" t="n">
-        <v>8.236791632367742</v>
+        <v>8.281636467519299</v>
       </c>
       <c r="D4" t="n">
-        <v>9.700745506950545</v>
+        <v>9.750573101563386</v>
       </c>
       <c r="E4" t="n">
-        <v>11.16469938153335</v>
+        <v>11.21950973560747</v>
       </c>
       <c r="F4" t="n">
-        <v>12.62865325611615</v>
+        <v>12.68844636965156</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.906758651768646</v>
+        <v>6.946620727458916</v>
       </c>
       <c r="C5" t="n">
-        <v>8.370712526351449</v>
+        <v>8.415557361503007</v>
       </c>
       <c r="D5" t="n">
-        <v>9.834666400934251</v>
+        <v>9.884493995547093</v>
       </c>
       <c r="E5" t="n">
-        <v>11.29862027551706</v>
+        <v>11.35343062959118</v>
       </c>
       <c r="F5" t="n">
-        <v>12.76257415009986</v>
+        <v>12.82236726363527</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.040679545752353</v>
+        <v>7.080541621442622</v>
       </c>
       <c r="C6" t="n">
-        <v>8.504633420335155</v>
+        <v>8.549478255486713</v>
       </c>
       <c r="D6" t="n">
-        <v>9.968587294917958</v>
+        <v>10.0184148895308</v>
       </c>
       <c r="E6" t="n">
-        <v>11.43254116950076</v>
+        <v>11.48735152357489</v>
       </c>
       <c r="F6" t="n">
-        <v>12.89649504408357</v>
+        <v>12.95628815761897</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.76</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.779999999999999</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.84</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.67</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.750573101563386</v>
+        <v>10.34633497656439</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.07159324337377</v>
+        <v>10.72735460046622</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.001526104005823</v>
+        <v>9.45728918746012</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.590500434799238</v>
+        <v>1.5917125156094</v>
       </c>
     </row>
     <row r="12">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>988.8358734426331</v>
+        <v>1080.512882373406</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>407.1345176037811</v>
+        <v>386.2269094339147</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>275.5195040774443</v>
+        <v>271.5240396054205</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1025.555895123859</v>
+        <v>1092.329831412741</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.07159324337377</v>
+        <v>10.72735460046622</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.07159324337377</v>
+        <v>10.72735460046622</v>
       </c>
     </row>
     <row r="15">
@@ -829,16 +829,16 @@
         <v>19150</v>
       </c>
       <c r="C2" t="n">
-        <v>18007</v>
+        <v>18028</v>
       </c>
       <c r="D2" t="n">
-        <v>0.577797784079314</v>
+        <v>0.5292518279608329</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1733393352237942</v>
+        <v>0.1587755483882499</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1688753966013065</v>
+        <v>0.1546866651475133</v>
       </c>
     </row>
     <row r="3">
@@ -851,16 +851,16 @@
         <v>19100</v>
       </c>
       <c r="C3" t="n">
-        <v>17987</v>
+        <v>18008</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5820715872699938</v>
+        <v>0.5284368501819465</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1746214761809981</v>
+        <v>0.158531055054584</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1657433703472989</v>
+        <v>0.150471018480138</v>
       </c>
     </row>
     <row r="4">
@@ -873,16 +873,16 @@
         <v>17325</v>
       </c>
       <c r="C4" t="n">
-        <v>17277</v>
+        <v>17298</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5227031346149993</v>
+        <v>0.4995051390314788</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1568109403844998</v>
+        <v>0.1498515417094436</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1450053831421083</v>
+        <v>0.1385699248198716</v>
       </c>
     </row>
     <row r="5">
@@ -895,16 +895,16 @@
         <v>16725</v>
       </c>
       <c r="C5" t="n">
-        <v>17037</v>
+        <v>17058</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5069814404365245</v>
+        <v>0.4897254056848417</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1520944321309573</v>
+        <v>0.1469176217054525</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1370220109287904</v>
+        <v>0.1323582177526599</v>
       </c>
     </row>
     <row r="6">
@@ -917,16 +917,16 @@
         <v>16125</v>
       </c>
       <c r="C6" t="n">
-        <v>16797</v>
+        <v>16818</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4912597462580496</v>
+        <v>0.4799456723382047</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1473779238774149</v>
+        <v>0.1439837017014614</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1293536568517866</v>
+        <v>0.1263745468258359</v>
       </c>
     </row>
     <row r="7">
@@ -939,16 +939,16 @@
         <v>15525</v>
       </c>
       <c r="C7" t="n">
-        <v>16557</v>
+        <v>16578</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4755380520795749</v>
+        <v>0.4701659389915678</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1426614156238725</v>
+        <v>0.1410497816974703</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1219893903826748</v>
+        <v>0.1206112865741427</v>
       </c>
     </row>
     <row r="8">
@@ -961,16 +961,16 @@
         <v>15125</v>
       </c>
       <c r="C8" t="n">
-        <v>16397</v>
+        <v>16418</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4660814995762893</v>
+        <v>0.4636461167604764</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1398244498728868</v>
+        <v>0.1390938350281429</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1164844373943996</v>
+        <v>0.115875779472131</v>
       </c>
     </row>
     <row r="9">
@@ -983,16 +983,16 @@
         <v>14825</v>
       </c>
       <c r="C9" t="n">
-        <v>16277</v>
+        <v>16298</v>
       </c>
       <c r="D9" t="n">
-        <v>0.458220652487052</v>
+        <v>0.458756250087158</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1374661957461156</v>
+        <v>0.1376268750261474</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1115706482802658</v>
+        <v>0.1117010591884972</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.096044293928631</v>
+        <v>1.05064849826079</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.99781384230859</v>
+        <v>10.63161369148366</v>
       </c>
       <c r="F11" t="n">
-        <v>7.905481810077192</v>
+        <v>8.40664068919933</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.001526104005823</v>
+        <v>9.45728918746012</v>
       </c>
     </row>
     <row r="13">
@@ -1055,7 +1055,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.544858045507796</v>
+        <v>7.119726804746892</v>
       </c>
       <c r="C2" t="n">
-        <v>8.013794679551886</v>
+        <v>8.652278592699094</v>
       </c>
       <c r="D2" t="n">
-        <v>9.482731313595973</v>
+        <v>10.1848303806513</v>
       </c>
       <c r="E2" t="n">
-        <v>10.95166794764006</v>
+        <v>11.71738216860352</v>
       </c>
       <c r="F2" t="n">
-        <v>12.42060458168415</v>
+        <v>13.24993395655572</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.678778939491503</v>
+        <v>7.200479102703433</v>
       </c>
       <c r="C3" t="n">
-        <v>8.147715573535594</v>
+        <v>8.733030890655636</v>
       </c>
       <c r="D3" t="n">
-        <v>9.61665220757968</v>
+        <v>10.26558267860785</v>
       </c>
       <c r="E3" t="n">
-        <v>11.08558884162377</v>
+        <v>11.79813446656006</v>
       </c>
       <c r="F3" t="n">
-        <v>12.55452547566786</v>
+        <v>13.33068625451226</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.812699833475209</v>
+        <v>7.281231400659974</v>
       </c>
       <c r="C4" t="n">
-        <v>8.281636467519299</v>
+        <v>8.813783188612176</v>
       </c>
       <c r="D4" t="n">
-        <v>9.750573101563386</v>
+        <v>10.34633497656439</v>
       </c>
       <c r="E4" t="n">
-        <v>11.21950973560747</v>
+        <v>11.8788867645166</v>
       </c>
       <c r="F4" t="n">
-        <v>12.68844636965156</v>
+        <v>13.4114385524688</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.946620727458916</v>
+        <v>7.361983698616514</v>
       </c>
       <c r="C5" t="n">
-        <v>8.415557361503007</v>
+        <v>8.894535486568717</v>
       </c>
       <c r="D5" t="n">
-        <v>9.884493995547093</v>
+        <v>10.42708727452093</v>
       </c>
       <c r="E5" t="n">
-        <v>11.35343062959118</v>
+        <v>11.95963906247314</v>
       </c>
       <c r="F5" t="n">
-        <v>12.82236726363527</v>
+        <v>13.49219085042534</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.080541621442622</v>
+        <v>7.442735996573055</v>
       </c>
       <c r="C6" t="n">
-        <v>8.549478255486713</v>
+        <v>8.975287784525257</v>
       </c>
       <c r="D6" t="n">
-        <v>10.0184148895308</v>
+        <v>10.50783957247747</v>
       </c>
       <c r="E6" t="n">
-        <v>11.48735152357489</v>
+        <v>12.04039136042968</v>
       </c>
       <c r="F6" t="n">
-        <v>12.95628815761897</v>
+        <v>13.57294314838188</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.81</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.83</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.84</v>
+        <v>10.43</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.34633497656439</v>
+        <v>9.750573101563386</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.72735460046622</v>
+        <v>10.07159324337377</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.45728918746012</v>
+        <v>9.001526104005823</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5917125156094</v>
+        <v>1.590500434799238</v>
       </c>
     </row>
     <row r="12">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1080.512882373406</v>
+        <v>988.8358734426331</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>386.2269094339147</v>
+        <v>407.1345176037811</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>271.5240396054205</v>
+        <v>275.5195040774443</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1092.329831412741</v>
+        <v>1025.555895123859</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.72735460046622</v>
+        <v>10.07159324337377</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.72735460046622</v>
+        <v>10.07159324337377</v>
       </c>
     </row>
     <row r="15">
@@ -829,16 +829,16 @@
         <v>19150</v>
       </c>
       <c r="C2" t="n">
-        <v>18028</v>
+        <v>18007</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5292518279608329</v>
+        <v>0.577797784079314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1587755483882499</v>
+        <v>0.1733393352237942</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1546866651475133</v>
+        <v>0.1688753966013065</v>
       </c>
     </row>
     <row r="3">
@@ -851,16 +851,16 @@
         <v>19100</v>
       </c>
       <c r="C3" t="n">
-        <v>18008</v>
+        <v>17987</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5284368501819465</v>
+        <v>0.5820715872699938</v>
       </c>
       <c r="E3" t="n">
-        <v>0.158531055054584</v>
+        <v>0.1746214761809981</v>
       </c>
       <c r="F3" t="n">
-        <v>0.150471018480138</v>
+        <v>0.1657433703472989</v>
       </c>
     </row>
     <row r="4">
@@ -873,16 +873,16 @@
         <v>17325</v>
       </c>
       <c r="C4" t="n">
-        <v>17298</v>
+        <v>17277</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4995051390314788</v>
+        <v>0.5227031346149993</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1498515417094436</v>
+        <v>0.1568109403844998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1385699248198716</v>
+        <v>0.1450053831421083</v>
       </c>
     </row>
     <row r="5">
@@ -895,16 +895,16 @@
         <v>16725</v>
       </c>
       <c r="C5" t="n">
-        <v>17058</v>
+        <v>17037</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4897254056848417</v>
+        <v>0.5069814404365245</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1469176217054525</v>
+        <v>0.1520944321309573</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1323582177526599</v>
+        <v>0.1370220109287904</v>
       </c>
     </row>
     <row r="6">
@@ -917,16 +917,16 @@
         <v>16125</v>
       </c>
       <c r="C6" t="n">
-        <v>16818</v>
+        <v>16797</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4799456723382047</v>
+        <v>0.4912597462580496</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1439837017014614</v>
+        <v>0.1473779238774149</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1263745468258359</v>
+        <v>0.1293536568517866</v>
       </c>
     </row>
     <row r="7">
@@ -939,16 +939,16 @@
         <v>15525</v>
       </c>
       <c r="C7" t="n">
-        <v>16578</v>
+        <v>16557</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4701659389915678</v>
+        <v>0.4755380520795749</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1410497816974703</v>
+        <v>0.1426614156238725</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1206112865741427</v>
+        <v>0.1219893903826748</v>
       </c>
     </row>
     <row r="8">
@@ -961,16 +961,16 @@
         <v>15125</v>
       </c>
       <c r="C8" t="n">
-        <v>16418</v>
+        <v>16397</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4636461167604764</v>
+        <v>0.4660814995762893</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1390938350281429</v>
+        <v>0.1398244498728868</v>
       </c>
       <c r="F8" t="n">
-        <v>0.115875779472131</v>
+        <v>0.1164844373943996</v>
       </c>
     </row>
     <row r="9">
@@ -983,16 +983,16 @@
         <v>14825</v>
       </c>
       <c r="C9" t="n">
-        <v>16298</v>
+        <v>16277</v>
       </c>
       <c r="D9" t="n">
-        <v>0.458756250087158</v>
+        <v>0.458220652487052</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1376268750261474</v>
+        <v>0.1374661957461156</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1117010591884972</v>
+        <v>0.1115706482802658</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.05064849826079</v>
+        <v>1.096044293928631</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.63161369148366</v>
+        <v>9.99781384230859</v>
       </c>
       <c r="F11" t="n">
-        <v>8.40664068919933</v>
+        <v>7.905481810077192</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.45728918746012</v>
+        <v>9.001526104005823</v>
       </c>
     </row>
     <row r="13">
@@ -1055,7 +1055,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.119726804746892</v>
+        <v>6.544858045507796</v>
       </c>
       <c r="C2" t="n">
-        <v>8.652278592699094</v>
+        <v>8.013794679551886</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1848303806513</v>
+        <v>9.482731313595973</v>
       </c>
       <c r="E2" t="n">
-        <v>11.71738216860352</v>
+        <v>10.95166794764006</v>
       </c>
       <c r="F2" t="n">
-        <v>13.24993395655572</v>
+        <v>12.42060458168415</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.200479102703433</v>
+        <v>6.678778939491503</v>
       </c>
       <c r="C3" t="n">
-        <v>8.733030890655636</v>
+        <v>8.147715573535594</v>
       </c>
       <c r="D3" t="n">
-        <v>10.26558267860785</v>
+        <v>9.61665220757968</v>
       </c>
       <c r="E3" t="n">
-        <v>11.79813446656006</v>
+        <v>11.08558884162377</v>
       </c>
       <c r="F3" t="n">
-        <v>13.33068625451226</v>
+        <v>12.55452547566786</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.281231400659974</v>
+        <v>6.812699833475209</v>
       </c>
       <c r="C4" t="n">
-        <v>8.813783188612176</v>
+        <v>8.281636467519299</v>
       </c>
       <c r="D4" t="n">
-        <v>10.34633497656439</v>
+        <v>9.750573101563386</v>
       </c>
       <c r="E4" t="n">
-        <v>11.8788867645166</v>
+        <v>11.21950973560747</v>
       </c>
       <c r="F4" t="n">
-        <v>13.4114385524688</v>
+        <v>12.68844636965156</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.361983698616514</v>
+        <v>6.946620727458916</v>
       </c>
       <c r="C5" t="n">
-        <v>8.894535486568717</v>
+        <v>8.415557361503007</v>
       </c>
       <c r="D5" t="n">
-        <v>10.42708727452093</v>
+        <v>9.884493995547093</v>
       </c>
       <c r="E5" t="n">
-        <v>11.95963906247314</v>
+        <v>11.35343062959118</v>
       </c>
       <c r="F5" t="n">
-        <v>13.49219085042534</v>
+        <v>12.82236726363527</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.442735996573055</v>
+        <v>7.080541621442622</v>
       </c>
       <c r="C6" t="n">
-        <v>8.975287784525257</v>
+        <v>8.549478255486713</v>
       </c>
       <c r="D6" t="n">
-        <v>10.50783957247747</v>
+        <v>10.0184148895308</v>
       </c>
       <c r="E6" t="n">
-        <v>12.04039136042968</v>
+        <v>11.48735152357489</v>
       </c>
       <c r="F6" t="n">
-        <v>13.57294314838188</v>
+        <v>12.95628815761897</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>10.41</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>10.42</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>10.43</v>
+        <v>9.84</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.81</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.750573101563386</v>
+        <v>9.697170811045414</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.07159324337377</v>
+        <v>10.0347243524999</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.001526104005823</v>
+        <v>8.909545880984945</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.590500434799238</v>
+        <v>1.5917125156094</v>
       </c>
     </row>
     <row r="12">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>988.8358734426331</v>
+        <v>1080.512882373406</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>407.1345176037811</v>
+        <v>386.2269094339147</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>275.5195040774443</v>
+        <v>271.5240396054205</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>171.775</v>
+        <v>134.537</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53.791</v>
+        <v>37.718</v>
       </c>
     </row>
     <row r="7">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-544</v>
+        <v>-511.448</v>
       </c>
     </row>
     <row r="8">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-227.5</v>
+        <v>-277.2</v>
       </c>
     </row>
     <row r="10">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1025.555895123859</v>
+        <v>1021.870831412741</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>101826580</v>
+        <v>101833473</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.07159324337377</v>
+        <v>10.0347243524999</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.07159324337377</v>
+        <v>10.0347243524999</v>
       </c>
     </row>
     <row r="15">
@@ -829,16 +829,16 @@
         <v>19150</v>
       </c>
       <c r="C2" t="n">
-        <v>18007</v>
+        <v>18028</v>
       </c>
       <c r="D2" t="n">
-        <v>0.577797784079314</v>
+        <v>0.5292160034647939</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1733393352237942</v>
+        <v>0.1587648010394382</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1688753966013065</v>
+        <v>0.1546761945708802</v>
       </c>
     </row>
     <row r="3">
@@ -851,16 +851,16 @@
         <v>19100</v>
       </c>
       <c r="C3" t="n">
-        <v>17987</v>
+        <v>18008</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5820715872699938</v>
+        <v>0.5284010808508907</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1746214761809981</v>
+        <v>0.1585203242552672</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1657433703472989</v>
+        <v>0.1504608332561657</v>
       </c>
     </row>
     <row r="4">
@@ -873,16 +873,16 @@
         <v>17325</v>
       </c>
       <c r="C4" t="n">
-        <v>17277</v>
+        <v>17298</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5227031346149993</v>
+        <v>0.4994713280573275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1568109403844998</v>
+        <v>0.1498413984171982</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1450053831421083</v>
+        <v>0.1385605451683322</v>
       </c>
     </row>
     <row r="5">
@@ -895,16 +895,16 @@
         <v>16725</v>
       </c>
       <c r="C5" t="n">
-        <v>17037</v>
+        <v>17058</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5069814404365245</v>
+        <v>0.489692256690489</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1520944321309573</v>
+        <v>0.1469076770071467</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1370220109287904</v>
+        <v>0.132349258564997</v>
       </c>
     </row>
     <row r="6">
@@ -917,16 +917,16 @@
         <v>16125</v>
       </c>
       <c r="C6" t="n">
-        <v>16797</v>
+        <v>16818</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4912597462580496</v>
+        <v>0.4799131853236508</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1473779238774149</v>
+        <v>0.1439739555970952</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1293536568517866</v>
+        <v>0.1263659926665245</v>
       </c>
     </row>
     <row r="7">
@@ -939,16 +939,16 @@
         <v>15525</v>
       </c>
       <c r="C7" t="n">
-        <v>16557</v>
+        <v>16578</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4755380520795749</v>
+        <v>0.4701341139568125</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1426614156238725</v>
+        <v>0.1410402341870438</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1219893903826748</v>
+        <v>0.1206031225238176</v>
       </c>
     </row>
     <row r="8">
@@ -961,16 +961,16 @@
         <v>15125</v>
       </c>
       <c r="C8" t="n">
-        <v>16397</v>
+        <v>16418</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4660814995762893</v>
+        <v>0.463614733045587</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1398244498728868</v>
+        <v>0.1390844199136761</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1164844373943996</v>
+        <v>0.1158679359632692</v>
       </c>
     </row>
     <row r="9">
@@ -983,16 +983,16 @@
         <v>14825</v>
       </c>
       <c r="C9" t="n">
-        <v>16277</v>
+        <v>16298</v>
       </c>
       <c r="D9" t="n">
-        <v>0.458220652487052</v>
+        <v>0.4587251973621679</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1374661957461156</v>
+        <v>0.1376175592086504</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1115706482802658</v>
+        <v>0.1116934982620326</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.096044293928631</v>
+        <v>1.050577380976019</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.99781384230859</v>
+        <v>9.938989924118136</v>
       </c>
       <c r="F11" t="n">
-        <v>7.905481810077192</v>
+        <v>7.858968500008927</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.001526104005823</v>
+        <v>8.909545880984945</v>
       </c>
     </row>
     <row r="13">
@@ -1053,7 +1053,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.544858045507796</v>
+        <v>6.470781044919811</v>
       </c>
       <c r="C2" t="n">
-        <v>8.013794679551886</v>
+        <v>8.003229096063643</v>
       </c>
       <c r="D2" t="n">
-        <v>9.482731313595973</v>
+        <v>9.535677147207483</v>
       </c>
       <c r="E2" t="n">
-        <v>10.95166794764006</v>
+        <v>11.06812519835132</v>
       </c>
       <c r="F2" t="n">
-        <v>12.42060458168415</v>
+        <v>12.60057324949515</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.678778939491503</v>
+        <v>6.551527876838776</v>
       </c>
       <c r="C3" t="n">
-        <v>8.147715573535594</v>
+        <v>8.083975927982609</v>
       </c>
       <c r="D3" t="n">
-        <v>9.61665220757968</v>
+        <v>9.616423979126449</v>
       </c>
       <c r="E3" t="n">
-        <v>11.08558884162377</v>
+        <v>11.14887203027029</v>
       </c>
       <c r="F3" t="n">
-        <v>12.55452547566786</v>
+        <v>12.68132008141412</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.812699833475209</v>
+        <v>6.632274708757742</v>
       </c>
       <c r="C4" t="n">
-        <v>8.281636467519299</v>
+        <v>8.164722759901574</v>
       </c>
       <c r="D4" t="n">
-        <v>9.750573101563386</v>
+        <v>9.697170811045414</v>
       </c>
       <c r="E4" t="n">
-        <v>11.21950973560747</v>
+        <v>11.22961886218926</v>
       </c>
       <c r="F4" t="n">
-        <v>12.68844636965156</v>
+        <v>12.76206691333309</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.946620727458916</v>
+        <v>6.713021540676708</v>
       </c>
       <c r="C5" t="n">
-        <v>8.415557361503007</v>
+        <v>8.245469591820539</v>
       </c>
       <c r="D5" t="n">
-        <v>9.884493995547093</v>
+        <v>9.777917642964379</v>
       </c>
       <c r="E5" t="n">
-        <v>11.35343062959118</v>
+        <v>11.31036569410822</v>
       </c>
       <c r="F5" t="n">
-        <v>12.82236726363527</v>
+        <v>12.84281374525205</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.080541621442622</v>
+        <v>6.793768372595673</v>
       </c>
       <c r="C6" t="n">
-        <v>8.549478255486713</v>
+        <v>8.326216423739506</v>
       </c>
       <c r="D6" t="n">
-        <v>10.0184148895308</v>
+        <v>9.858664474883346</v>
       </c>
       <c r="E6" t="n">
-        <v>11.48735152357489</v>
+        <v>11.39111252602719</v>
       </c>
       <c r="F6" t="n">
-        <v>12.95628815761897</v>
+        <v>12.92356057717102</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.81</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.83</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.84</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.697170811045414</v>
+        <v>10.20698755700007</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.0347243524999</v>
+        <v>10.57911476672499</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.909545880984945</v>
+        <v>9.338690734308569</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5917125156094</v>
+        <v>1.592123887097517</v>
       </c>
     </row>
     <row r="12">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1080.512882373406</v>
+        <v>1111.098255558827</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>386.2269094339147</v>
+        <v>409.3135005827698</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>271.5240396054205</v>
+        <v>273.2892418195938</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1021.870831412741</v>
+        <v>1077.307997961191</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.0347243524999</v>
+        <v>10.57911476672499</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.0347243524999</v>
+        <v>10.57911476672499</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.938989924118136</v>
+        <v>10.48171590312744</v>
       </c>
       <c r="F11" t="n">
-        <v>7.858968500008927</v>
+        <v>8.28811335333255</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8.909545880984945</v>
+        <v>9.338690734308569</v>
       </c>
     </row>
     <row r="13">
@@ -1055,7 +1055,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.470781044919811</v>
+        <v>6.878634441683529</v>
       </c>
       <c r="C2" t="n">
-        <v>8.003229096063643</v>
+        <v>8.462064167422827</v>
       </c>
       <c r="D2" t="n">
-        <v>9.535677147207483</v>
+        <v>10.04549389316213</v>
       </c>
       <c r="E2" t="n">
-        <v>11.06812519835132</v>
+        <v>11.62892361890143</v>
       </c>
       <c r="F2" t="n">
-        <v>12.60057324949515</v>
+        <v>13.21235334464073</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.551527876838776</v>
+        <v>6.959381273602494</v>
       </c>
       <c r="C3" t="n">
-        <v>8.083975927982609</v>
+        <v>8.542810999341793</v>
       </c>
       <c r="D3" t="n">
-        <v>9.616423979126449</v>
+        <v>10.1262407250811</v>
       </c>
       <c r="E3" t="n">
-        <v>11.14887203027029</v>
+        <v>11.70967045082039</v>
       </c>
       <c r="F3" t="n">
-        <v>12.68132008141412</v>
+        <v>13.29310017655969</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.632274708757742</v>
+        <v>7.040128105521459</v>
       </c>
       <c r="C4" t="n">
-        <v>8.164722759901574</v>
+        <v>8.623557831260758</v>
       </c>
       <c r="D4" t="n">
-        <v>9.697170811045414</v>
+        <v>10.20698755700007</v>
       </c>
       <c r="E4" t="n">
-        <v>11.22961886218926</v>
+        <v>11.79041728273936</v>
       </c>
       <c r="F4" t="n">
-        <v>12.76206691333309</v>
+        <v>13.37384700847866</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.713021540676708</v>
+        <v>7.120874937440425</v>
       </c>
       <c r="C5" t="n">
-        <v>8.245469591820539</v>
+        <v>8.704304663179725</v>
       </c>
       <c r="D5" t="n">
-        <v>9.777917642964379</v>
+        <v>10.28773438891903</v>
       </c>
       <c r="E5" t="n">
-        <v>11.31036569410822</v>
+        <v>11.87116411465833</v>
       </c>
       <c r="F5" t="n">
-        <v>12.84281374525205</v>
+        <v>13.45459384039762</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.793768372595673</v>
+        <v>7.201621769359391</v>
       </c>
       <c r="C6" t="n">
-        <v>8.326216423739506</v>
+        <v>8.78505149509869</v>
       </c>
       <c r="D6" t="n">
-        <v>9.858664474883346</v>
+        <v>10.368481220838</v>
       </c>
       <c r="E6" t="n">
-        <v>11.39111252602719</v>
+        <v>11.95191094657729</v>
       </c>
       <c r="F6" t="n">
-        <v>12.92356057717102</v>
+        <v>13.53534067231659</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.76</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.779999999999999</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.779999999999999</v>
+        <v>10.29</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.20698755700007</v>
+        <v>10.2395664448824</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.338690734308569</v>
+        <v>9.447287027249699</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19150</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18075</v>
+        <v>18568.75</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.592123887097517</v>
+        <v>1.507906630874804</v>
       </c>
     </row>
     <row r="12">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19150</v>
+        <v>20500</v>
       </c>
       <c r="C2" t="n">
-        <v>18028</v>
+        <v>18568</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5292160034647939</v>
+        <v>0.55121891404018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1587648010394382</v>
+        <v>0.165365674212054</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1546761945708802</v>
+        <v>0.1611070780948145</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19100</v>
+        <v>20325</v>
       </c>
       <c r="C3" t="n">
-        <v>18008</v>
+        <v>18498</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5284010808508907</v>
+        <v>0.548366684891519</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1585203242552672</v>
+        <v>0.1645100054674557</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1504608332561657</v>
+        <v>0.1561459870707229</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17325</v>
+        <v>16250</v>
       </c>
       <c r="C4" t="n">
-        <v>17298</v>
+        <v>16868</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4994713280573275</v>
+        <v>0.4819504918584088</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1498413984171982</v>
+        <v>0.1445851475575226</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1385605451683322</v>
+        <v>0.1337000126829749</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16725</v>
+        <v>17200</v>
       </c>
       <c r="C5" t="n">
-        <v>17058</v>
+        <v>17248</v>
       </c>
       <c r="D5" t="n">
-        <v>0.489692256690489</v>
+        <v>0.4974340215225695</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1469076770071467</v>
+        <v>0.1492302064567708</v>
       </c>
       <c r="F5" t="n">
-        <v>0.132349258564997</v>
+        <v>0.1344416274385323</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16125</v>
+        <v>17225</v>
       </c>
       <c r="C6" t="n">
-        <v>16818</v>
+        <v>17258</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4799131853236508</v>
+        <v>0.497841482829521</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1439739555970952</v>
+        <v>0.1493524448488563</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1263659926665245</v>
+        <v>0.1310866946193625</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15525</v>
+        <v>17225</v>
       </c>
       <c r="C7" t="n">
-        <v>16578</v>
+        <v>17258</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4701341139568125</v>
+        <v>0.497841482829521</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1410402341870438</v>
+        <v>0.1493524448488563</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1206031225238176</v>
+        <v>0.1277108713634919</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15125</v>
+        <v>16825</v>
       </c>
       <c r="C8" t="n">
-        <v>16418</v>
+        <v>17098</v>
       </c>
       <c r="D8" t="n">
-        <v>0.463614733045587</v>
+        <v>0.4913221019182956</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1390844199136761</v>
+        <v>0.1473966305754887</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1158679359632692</v>
+        <v>0.1227926417877884</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14825</v>
+        <v>16525</v>
       </c>
       <c r="C9" t="n">
-        <v>16298</v>
+        <v>16978</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4587251973621679</v>
+        <v>0.4864325662348764</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1376175592086504</v>
+        <v>0.1459297698704629</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1116934982620326</v>
+        <v>0.1184398749050101</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.050577380976019</v>
+        <v>1.085424787962697</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.48171590312744</v>
+        <v>10.57498379628866</v>
       </c>
       <c r="F11" t="n">
-        <v>8.28811335333255</v>
+        <v>8.361862239287001</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.338690734308569</v>
+        <v>9.447287027249699</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18075</v>
+        <v>18568.75</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.878634441683529</v>
+        <v>6.901439663201165</v>
       </c>
       <c r="C2" t="n">
-        <v>8.462064167422827</v>
+        <v>8.484869388940464</v>
       </c>
       <c r="D2" t="n">
-        <v>10.04549389316213</v>
+        <v>10.06829911467977</v>
       </c>
       <c r="E2" t="n">
-        <v>11.62892361890143</v>
+        <v>11.65172884041907</v>
       </c>
       <c r="F2" t="n">
-        <v>13.21235334464073</v>
+        <v>13.23515856615836</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.959381273602494</v>
+        <v>6.987073328302482</v>
       </c>
       <c r="C3" t="n">
-        <v>8.542810999341793</v>
+        <v>8.570503054041781</v>
       </c>
       <c r="D3" t="n">
-        <v>10.1262407250811</v>
+        <v>10.15393277978109</v>
       </c>
       <c r="E3" t="n">
-        <v>11.70967045082039</v>
+        <v>11.73736250552038</v>
       </c>
       <c r="F3" t="n">
-        <v>13.29310017655969</v>
+        <v>13.32079223125968</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.040128105521459</v>
+        <v>7.072706993403798</v>
       </c>
       <c r="C4" t="n">
-        <v>8.623557831260758</v>
+        <v>8.656136719143097</v>
       </c>
       <c r="D4" t="n">
-        <v>10.20698755700007</v>
+        <v>10.2395664448824</v>
       </c>
       <c r="E4" t="n">
-        <v>11.79041728273936</v>
+        <v>11.8229961706217</v>
       </c>
       <c r="F4" t="n">
-        <v>13.37384700847866</v>
+        <v>13.406425896361</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.120874937440425</v>
+        <v>7.158340658505114</v>
       </c>
       <c r="C5" t="n">
-        <v>8.704304663179725</v>
+        <v>8.741770384244415</v>
       </c>
       <c r="D5" t="n">
-        <v>10.28773438891903</v>
+        <v>10.32520010998372</v>
       </c>
       <c r="E5" t="n">
-        <v>11.87116411465833</v>
+        <v>11.90862983572302</v>
       </c>
       <c r="F5" t="n">
-        <v>13.45459384039762</v>
+        <v>13.49205956146231</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.201621769359391</v>
+        <v>7.243974323606431</v>
       </c>
       <c r="C6" t="n">
-        <v>8.78505149509869</v>
+        <v>8.827404049345731</v>
       </c>
       <c r="D6" t="n">
-        <v>10.368481220838</v>
+        <v>10.41083377508504</v>
       </c>
       <c r="E6" t="n">
-        <v>11.95191094657729</v>
+        <v>11.99426350082433</v>
       </c>
       <c r="F6" t="n">
-        <v>13.53534067231659</v>
+        <v>13.57769322656363</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>10.27</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>10.29</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>10.29</v>
+        <v>10.33</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.6</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.46</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.75</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.39</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.2395664448824</v>
+        <v>10.34191192872632</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.57911476672499</v>
+        <v>10.6543121239173</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.447287027249699</v>
+        <v>9.612978139947362</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18300</v>
+        <v>19583</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18568.75</v>
+        <v>19434.5</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.507906630874804</v>
+        <v>1.624034519788003</v>
       </c>
     </row>
     <row r="12">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1111.098255558827</v>
+        <v>1118.75586360214</v>
       </c>
     </row>
     <row r="3">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1077.307997961191</v>
+        <v>1084.965606004504</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.57911476672499</v>
+        <v>10.6543121239173</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.57911476672499</v>
+        <v>10.6543121239173</v>
       </c>
     </row>
     <row r="15">
@@ -782,7 +782,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20500</v>
+        <v>20563</v>
       </c>
       <c r="C2" t="n">
-        <v>18568</v>
+        <v>18593.2</v>
       </c>
       <c r="D2" t="n">
-        <v>0.55121891404018</v>
+        <v>0.5522457165336981</v>
       </c>
       <c r="E2" t="n">
-        <v>0.165365674212054</v>
+        <v>0.1656737149601094</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1611070780948145</v>
+        <v>0.1614071859925982</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20325</v>
+        <v>21791</v>
       </c>
       <c r="C3" t="n">
-        <v>18498</v>
+        <v>19084.4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.548366684891519</v>
+        <v>0.5722602159311604</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1645100054674557</v>
+        <v>0.1716780647793481</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1561459870707229</v>
+        <v>0.1629496078806338</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16250</v>
+        <v>17375</v>
       </c>
       <c r="C4" t="n">
-        <v>16868</v>
+        <v>17318</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4819504918584088</v>
+        <v>0.5002862506712306</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1445851475575226</v>
+        <v>0.1500858752013692</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1337000126829749</v>
+        <v>0.1387866164467209</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17200</v>
+        <v>18009</v>
       </c>
       <c r="C5" t="n">
-        <v>17248</v>
+        <v>17571.6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4974340215225695</v>
+        <v>0.5106194694155231</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1492302064567708</v>
+        <v>0.1531858408246569</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1344416274385323</v>
+        <v>0.1380052620041954</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17225</v>
+        <v>18008</v>
       </c>
       <c r="C6" t="n">
-        <v>17258</v>
+        <v>17571.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.497841482829521</v>
+        <v>0.510603170963245</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1493524448488563</v>
+        <v>0.1531809512889735</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1310866946193625</v>
+        <v>0.1344469761003372</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17225</v>
+        <v>18008</v>
       </c>
       <c r="C7" t="n">
-        <v>17258</v>
+        <v>17571.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.497841482829521</v>
+        <v>0.510603170963245</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1493524448488563</v>
+        <v>0.1531809512889735</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1277108713634919</v>
+        <v>0.1309846168584714</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16825</v>
+        <v>17608</v>
       </c>
       <c r="C8" t="n">
-        <v>17098</v>
+        <v>17411.2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4913221019182956</v>
+        <v>0.5040837900520194</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1473966305754887</v>
+        <v>0.1512251370156058</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1227926417877884</v>
+        <v>0.1259820798234345</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16525</v>
+        <v>17308</v>
       </c>
       <c r="C9" t="n">
-        <v>16978</v>
+        <v>17291.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4864325662348764</v>
+        <v>0.4991942543686002</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1459297698704629</v>
+        <v>0.1497582763105801</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1184398749050101</v>
+        <v>0.1215471766176285</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.085424787962697</v>
+        <v>1.11410952172402</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.57498379628866</v>
+        <v>10.74825144837133</v>
       </c>
       <c r="F11" t="n">
-        <v>8.361862239287001</v>
+        <v>8.498868618223343</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.447287027249699</v>
+        <v>9.612978139947362</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18568.75</v>
+        <v>19434.5</v>
       </c>
     </row>
   </sheetData>
@@ -1053,7 +1053,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.901439663201165</v>
+        <v>6.980670649904301</v>
       </c>
       <c r="C2" t="n">
-        <v>8.484869388940464</v>
+        <v>8.571689523655996</v>
       </c>
       <c r="D2" t="n">
-        <v>10.06829911467977</v>
+        <v>10.1627083974077</v>
       </c>
       <c r="E2" t="n">
-        <v>11.65172884041907</v>
+        <v>11.75372727115939</v>
       </c>
       <c r="F2" t="n">
-        <v>13.23515856615836</v>
+        <v>13.34474614491108</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.987073328302482</v>
+        <v>7.070272415563608</v>
       </c>
       <c r="C3" t="n">
-        <v>8.570503054041781</v>
+        <v>8.661291289315304</v>
       </c>
       <c r="D3" t="n">
-        <v>10.15393277978109</v>
+        <v>10.25231016306701</v>
       </c>
       <c r="E3" t="n">
-        <v>11.73736250552038</v>
+        <v>11.8433290368187</v>
       </c>
       <c r="F3" t="n">
-        <v>13.32079223125968</v>
+        <v>13.43434791057039</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.072706993403798</v>
+        <v>7.159874181222916</v>
       </c>
       <c r="C4" t="n">
-        <v>8.656136719143097</v>
+        <v>8.750893054974611</v>
       </c>
       <c r="D4" t="n">
-        <v>10.2395664448824</v>
+        <v>10.34191192872632</v>
       </c>
       <c r="E4" t="n">
-        <v>11.8229961706217</v>
+        <v>11.932930802478</v>
       </c>
       <c r="F4" t="n">
-        <v>13.406425896361</v>
+        <v>13.5239496762297</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.158340658505114</v>
+        <v>7.249475946882223</v>
       </c>
       <c r="C5" t="n">
-        <v>8.741770384244415</v>
+        <v>8.840494820633918</v>
       </c>
       <c r="D5" t="n">
-        <v>10.32520010998372</v>
+        <v>10.43151369438562</v>
       </c>
       <c r="E5" t="n">
-        <v>11.90862983572302</v>
+        <v>12.02253256813731</v>
       </c>
       <c r="F5" t="n">
-        <v>13.49205956146231</v>
+        <v>13.61355144188901</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.243974323606431</v>
+        <v>7.339077712541531</v>
       </c>
       <c r="C6" t="n">
-        <v>8.827404049345731</v>
+        <v>8.930096586293226</v>
       </c>
       <c r="D6" t="n">
-        <v>10.41083377508504</v>
+        <v>10.52111546004493</v>
       </c>
       <c r="E6" t="n">
-        <v>11.99426350082433</v>
+        <v>12.11213433379662</v>
       </c>
       <c r="F6" t="n">
-        <v>13.57769322656363</v>
+        <v>13.70315320754831</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>10.3</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>10.32</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>10.33</v>
+        <v>10.43</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sb_fv_report.xlsx
+++ b/outputs/sb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.34191192872632</v>
+        <v>10.42003150593374</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.6543121239173</v>
+        <v>10.71861602030806</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.612978139947362</v>
+        <v>9.723334305727017</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19583</v>
+        <v>20550</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19434.5</v>
+        <v>20291.75</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.624034519788003</v>
+        <v>1.7050820897164</v>
       </c>
     </row>
     <row r="12">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1118.75586360214</v>
+        <v>1125.304152699043</v>
       </c>
     </row>
     <row r="3">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1084.965606004504</v>
+        <v>1091.513895101408</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.6543121239173</v>
+        <v>10.71861602030806</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.6543121239173</v>
+        <v>10.71861602030806</v>
       </c>
     </row>
     <row r="15">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20563</v>
+        <v>21900</v>
       </c>
       <c r="C2" t="n">
-        <v>18593.2</v>
+        <v>19128</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5522457165336981</v>
+        <v>0.5740367472294694</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1656737149601094</v>
+        <v>0.1722110241688408</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1614071859925982</v>
+        <v>0.1677761424900057</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21791</v>
+        <v>22900</v>
       </c>
       <c r="C3" t="n">
-        <v>19084.4</v>
+        <v>19528</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5722602159311604</v>
+        <v>0.5903351995075332</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1716780647793481</v>
+        <v>0.1771005598522599</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1629496078806338</v>
+        <v>0.1680964124360166</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17375</v>
+        <v>18200</v>
       </c>
       <c r="C4" t="n">
-        <v>17318</v>
+        <v>17648</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5002862506712306</v>
+        <v>0.5137324738006334</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1500858752013692</v>
+        <v>0.15411974214019</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1387866164467209</v>
+        <v>0.1425167925401347</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18009</v>
+        <v>18167</v>
       </c>
       <c r="C5" t="n">
-        <v>17571.6</v>
+        <v>17634.8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5106194694155231</v>
+        <v>0.5131946248754572</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1531858408246569</v>
+        <v>0.1539583874626372</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1380052620041954</v>
+        <v>0.1387012499663398</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18008</v>
+        <v>18167</v>
       </c>
       <c r="C6" t="n">
-        <v>17571.2</v>
+        <v>17634.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.510603170963245</v>
+        <v>0.5131946248754572</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1531809512889735</v>
+        <v>0.1539583874626372</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1344469761003372</v>
+        <v>0.1351293321098838</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18008</v>
+        <v>18166</v>
       </c>
       <c r="C7" t="n">
-        <v>17571.2</v>
+        <v>17634.4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.510603170963245</v>
+        <v>0.5131783264231791</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1531809512889735</v>
+        <v>0.1539534979269537</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1309846168584714</v>
+        <v>0.1316452193976882</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17608</v>
+        <v>17766</v>
       </c>
       <c r="C8" t="n">
-        <v>17411.2</v>
+        <v>17474.4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5040837900520194</v>
+        <v>0.5066589455119537</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1512251370156058</v>
+        <v>0.1519976836535861</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1259820798234345</v>
+        <v>0.1266256701294781</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17308</v>
+        <v>17466</v>
       </c>
       <c r="C9" t="n">
-        <v>17291.2</v>
+        <v>17354.4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4991942543686002</v>
+        <v>0.5017694098285345</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1497582763105801</v>
+        <v>0.1505308229485603</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1215471766176285</v>
+        <v>0.1221741927997405</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.11410952172402</v>
+        <v>1.132665011869287</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.74825144837133</v>
+        <v>10.86434887135456</v>
       </c>
       <c r="F11" t="n">
-        <v>8.498868618223343</v>
+        <v>8.590669293857729</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.612978139947362</v>
+        <v>9.723334305727017</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19434.5</v>
+        <v>20291.75</v>
       </c>
     </row>
   </sheetData>
@@ -1053,7 +1053,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.980670649904301</v>
+        <v>7.041510314948464</v>
       </c>
       <c r="C2" t="n">
-        <v>8.571689523655996</v>
+        <v>8.638685149699128</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1627083974077</v>
+        <v>10.23585998444979</v>
       </c>
       <c r="E2" t="n">
-        <v>11.75372727115939</v>
+        <v>11.83303481920045</v>
       </c>
       <c r="F2" t="n">
-        <v>13.34474614491108</v>
+        <v>13.43020965395111</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.070272415563608</v>
+        <v>7.13359607569044</v>
       </c>
       <c r="C3" t="n">
-        <v>8.661291289315304</v>
+        <v>8.730770910441102</v>
       </c>
       <c r="D3" t="n">
-        <v>10.25231016306701</v>
+        <v>10.32794574519177</v>
       </c>
       <c r="E3" t="n">
-        <v>11.8433290368187</v>
+        <v>11.92512057994242</v>
       </c>
       <c r="F3" t="n">
-        <v>13.43434791057039</v>
+        <v>13.52229541469308</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.159874181222916</v>
+        <v>7.225681836432415</v>
       </c>
       <c r="C4" t="n">
-        <v>8.750893054974611</v>
+        <v>8.822856671183077</v>
       </c>
       <c r="D4" t="n">
-        <v>10.34191192872632</v>
+        <v>10.42003150593374</v>
       </c>
       <c r="E4" t="n">
-        <v>11.932930802478</v>
+        <v>12.0172063406844</v>
       </c>
       <c r="F4" t="n">
-        <v>13.5239496762297</v>
+        <v>13.61438117543506</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.249475946882223</v>
+        <v>7.31776759717439</v>
       </c>
       <c r="C5" t="n">
-        <v>8.840494820633918</v>
+        <v>8.914942431925052</v>
       </c>
       <c r="D5" t="n">
-        <v>10.43151369438562</v>
+        <v>10.51211726667572</v>
       </c>
       <c r="E5" t="n">
-        <v>12.02253256813731</v>
+        <v>12.10929210142637</v>
       </c>
       <c r="F5" t="n">
-        <v>13.61355144188901</v>
+        <v>13.70646693617703</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.339077712541531</v>
+        <v>7.409853357916364</v>
       </c>
       <c r="C6" t="n">
-        <v>8.930096586293226</v>
+        <v>9.007028192667027</v>
       </c>
       <c r="D6" t="n">
-        <v>10.52111546004493</v>
+        <v>10.60420302741769</v>
       </c>
       <c r="E6" t="n">
-        <v>12.11213433379662</v>
+        <v>12.20137786216835</v>
       </c>
       <c r="F6" t="n">
-        <v>13.70315320754831</v>
+        <v>13.79855269691901</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>10.41</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>10.42</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>10.43</v>
+        <v>10.51</v>
       </c>
     </row>
   </sheetData>
